--- a/Assets/Data/Commodore/C128/250477/Data C128DCR 250477 v2.0.0.xlsx
+++ b/Assets/Data/Commodore/C128/250477/Data C128DCR 250477 v2.0.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dennis\AppData\Local\Classic-Repair-Toolbox\Data\Commodore\C128\250477\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.20.10\all\mydir\http\classic-repair-toolbox.dk\public_html\app-data\Data\Commodore\C128\250477\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EAF949A-9258-4C9E-8436-F0014136063C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB10B76-7433-4430-8522-4935D5125F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Board schematics" sheetId="5" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4397" uniqueCount="1908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4401" uniqueCount="1911">
   <si>
     <t>Name</t>
   </si>
@@ -5824,6 +5824,24 @@
     <t>Commodore/Shared files/Component local files/5710.txt</t>
   </si>
   <si>
+    <t>Forum64; Repair Corner (primarily German)</t>
+  </si>
+  <si>
+    <t>https://www.forum64.de/index.php?board/183-repair-corner/</t>
+  </si>
+  <si>
+    <t>4a9216da-655f-4dc4-9b84-6bb382163f78</t>
+  </si>
+  <si>
+    <t>Zimmers; Character ROMs</t>
+  </si>
+  <si>
+    <t>https://www.zimmers.net/anonftp/pub/cbm/firmware/characters/</t>
+  </si>
+  <si>
+    <t>85544409-f5d1-4016-89c1-2b7c926ead4a</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve"># Revision date: </t>
     </r>
@@ -5836,17 +5854,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-May-12</t>
+      <t>2026-June-10</t>
     </r>
-  </si>
-  <si>
-    <t>Forum64; Repair Corner (primarily German)</t>
-  </si>
-  <si>
-    <t>https://www.forum64.de/index.php?board/183-repair-corner/</t>
-  </si>
-  <si>
-    <t>4a9216da-655f-4dc4-9b84-6bb382163f78</t>
   </si>
 </sst>
 </file>
@@ -6006,7 +6015,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -6168,6 +6177,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6513,7 +6526,7 @@
     </row>
     <row r="3" spans="1:11" s="8" customFormat="1" ht="21">
       <c r="A3" s="8" t="s">
-        <v>1904</v>
+        <v>1910</v>
       </c>
       <c r="I3"/>
     </row>
@@ -23401,7 +23414,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9014B11-7294-4050-ABF4-8B4EFBD7F103}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
@@ -23488,56 +23501,67 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B11" t="s">
-        <v>322</v>
-      </c>
-      <c r="C11" t="s">
-        <v>321</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1453</v>
+    <row r="11" spans="1:4" s="60" customFormat="1">
+      <c r="A11" s="59" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="60" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C11" s="60" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D11" s="60" t="s">
+        <v>1909</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" t="s">
+        <v>322</v>
+      </c>
+      <c r="C12" t="s">
+        <v>321</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="9" t="s">
         <v>590</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>705</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>704</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" t="s">
         <v>1454</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
         <v>331</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>281</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" t="s">
         <v>280</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D14" t="s">
         <v>1455</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="19"/>
-    </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="16"/>
+      <c r="A16" s="19"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="D17" s="1"/>
+      <c r="A17" s="16"/>
     </row>
     <row r="18" spans="1:4">
       <c r="D18" s="1"/>
@@ -23546,32 +23570,32 @@
       <c r="D19" s="1"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="17"/>
       <c r="D20" s="1"/>
     </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="17"/>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="18"/>
+    <row r="21" spans="1:4">
+      <c r="A21" s="17"/>
+      <c r="D21" s="1"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="17"/>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="9"/>
+      <c r="A28" s="18"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="9"/>
     </row>
-    <row r="34" spans="4:4">
-      <c r="D34" s="53"/>
-    </row>
-    <row r="36" spans="4:4">
-      <c r="D36" s="53"/>
-    </row>
-    <row r="49" spans="4:4">
-      <c r="D49" s="4"/>
-    </row>
-    <row r="55" spans="4:4">
-      <c r="D55" s="1"/>
+    <row r="30" spans="1:4">
+      <c r="A30" s="9"/>
+    </row>
+    <row r="35" spans="4:4">
+      <c r="D35" s="53"/>
+    </row>
+    <row r="37" spans="4:4">
+      <c r="D37" s="53"/>
+    </row>
+    <row r="50" spans="4:4">
+      <c r="D50" s="4"/>
     </row>
     <row r="56" spans="4:4">
       <c r="D56" s="1"/>
@@ -23584,6 +23608,9 @@
     </row>
     <row r="59" spans="4:4">
       <c r="D59" s="1"/>
+    </row>
+    <row r="60" spans="4:4">
+      <c r="D60" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24102,13 +24129,13 @@
         <v>130</v>
       </c>
       <c r="B19" t="s">
+        <v>1904</v>
+      </c>
+      <c r="C19" t="s">
         <v>1905</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" s="1" t="s">
         <v>1906</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>1907</v>
       </c>
     </row>
     <row r="20" spans="1:4">

--- a/Assets/Data/Commodore/C128/250477/Data C128DCR 250477 v2.0.0.xlsx
+++ b/Assets/Data/Commodore/C128/250477/Data C128DCR 250477 v2.0.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.20.10\all\mydir\http\classic-repair-toolbox.dk\public_html\app-data\Data\Commodore\C128\250477\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB10B76-7433-4430-8522-4935D5125F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A1BDE9-36F7-47C7-B921-D93EC191D1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Board schematics" sheetId="5" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4401" uniqueCount="1911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4401" uniqueCount="1914">
   <si>
     <t>Name</t>
   </si>
@@ -5198,18 +5198,6 @@
     <t>382eabc1-db16-4658-8b8d-ba2966fe0f95</t>
   </si>
   <si>
-    <t>Resistor pack, 8 pin</t>
-  </si>
-  <si>
-    <t>Resistor pack, 6 pin</t>
-  </si>
-  <si>
-    <t>Resistor pack, 9 pin</t>
-  </si>
-  <si>
-    <t>Resistor pack, 7 pin</t>
-  </si>
-  <si>
     <t>9e2b8f16-82c7-4493-8cc8-4f1a71ca060a</t>
   </si>
   <si>
@@ -5235,9 +5223,6 @@
   </si>
   <si>
     <t>fc426b09-ae14-415c-a668-fd777dce0aef</t>
-  </si>
-  <si>
-    <t>Resistor packs must be mounted with GND pin at its designated position</t>
   </si>
   <si>
     <t>349608fd-68db-448c-8269-9133fb6695e4</t>
@@ -5575,18 +5560,6 @@
     <t>Generic shared files/Component images/resistor_470_5.png</t>
   </si>
   <si>
-    <t>Generic shared files/Component images/resistor_pack_7pin.png</t>
-  </si>
-  <si>
-    <t>Generic shared files/Component images/resistor_pack_8pin.png</t>
-  </si>
-  <si>
-    <t>Generic shared files/Component images/resistor_pack_9pin.png</t>
-  </si>
-  <si>
-    <t>Generic shared files/Component images/resistor_pack_6pin.png</t>
-  </si>
-  <si>
     <t>Generic shared files/Component local files/1N4371.pdf</t>
   </si>
   <si>
@@ -5840,6 +5813,44 @@
   </si>
   <si>
     <t>85544409-f5d1-4016-89c1-2b7c926ead4a</t>
+  </si>
+  <si>
+    <t>Resistor pack, 7 pin, bussed</t>
+  </si>
+  <si>
+    <t>Resistor pack, 8 pin, bussed</t>
+  </si>
+  <si>
+    <t>Resistor pack, 9 pin, bussed</t>
+  </si>
+  <si>
+    <t>Resistor pack, 8 pin, isolated</t>
+  </si>
+  <si>
+    <t>Resistor pack, 6 pin, bussed</t>
+  </si>
+  <si>
+    <t>Generic shared files/Component images/resistor_pack_7pin_bussed.png</t>
+  </si>
+  <si>
+    <t>Generic shared files/Component images/resistor_pack_8pin_bussed.png</t>
+  </si>
+  <si>
+    <t>Generic shared files/Component images/resistor_pack_9pin_bussed.png</t>
+  </si>
+  <si>
+    <t>Generic shared files/Component images/resistor_pack_8pin_isolated.png</t>
+  </si>
+  <si>
+    <t>Generic shared files/Component images/resistor_pack_6pin_bussed.png</t>
+  </si>
+  <si>
+    <t>Resistor packs must be mounted with GND pin at its designated position.
+Note this resistor pack is isolated, and by then each two pin is its own pair (pin 1+2, pin 3+4 and pin 5+6 etc).</t>
+  </si>
+  <si>
+    <t>Resistor packs must be mounted with GND pin at its designated position.
+Note this resistor pack is bussed, and by then each pin share pin 1 as GROUND.</t>
   </si>
   <si>
     <r>
@@ -5854,7 +5865,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-June-10</t>
+      <t>2026-August-21</t>
     </r>
   </si>
 </sst>
@@ -6174,13 +6185,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6526,7 +6537,7 @@
     </row>
     <row r="3" spans="1:11" s="8" customFormat="1" ht="21">
       <c r="A3" s="8" t="s">
-        <v>1910</v>
+        <v>1913</v>
       </c>
       <c r="I3"/>
     </row>
@@ -6579,13 +6590,13 @@
         <v>284</v>
       </c>
       <c r="B8" s="6"/>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="60" t="s">
         <v>283</v>
       </c>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
       <c r="H8" s="55"/>
       <c r="I8" s="6"/>
     </row>
@@ -6597,16 +6608,16 @@
         <v>260</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>1738</v>
+        <v>1733</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>1739</v>
+        <v>1734</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>1740</v>
+        <v>1735</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>1741</v>
+        <v>1736</v>
       </c>
       <c r="G9" s="33" t="s">
         <v>282</v>
@@ -6623,7 +6634,7 @@
         <v>465</v>
       </c>
       <c r="B10" t="s">
-        <v>1742</v>
+        <v>1737</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>5</v>
@@ -6648,7 +6659,7 @@
         <v>256</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>1743</v>
+        <v>1738</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>5</v>
@@ -6673,7 +6684,7 @@
         <v>444</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>1744</v>
+        <v>1739</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>5</v>
@@ -6699,7 +6710,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>1745</v>
+        <v>1740</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>5</v>
@@ -6724,7 +6735,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>1746</v>
+        <v>1741</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>5</v>
@@ -6749,7 +6760,7 @@
         <v>447</v>
       </c>
       <c r="B15" t="s">
-        <v>1747</v>
+        <v>1742</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>5</v>
@@ -13268,7 +13279,7 @@
         <v>648</v>
       </c>
       <c r="G378" s="1" t="s">
-        <v>1699</v>
+        <v>1901</v>
       </c>
       <c r="H378" t="s">
         <v>1136</v>
@@ -13285,7 +13296,7 @@
         <v>648</v>
       </c>
       <c r="G379" s="1" t="s">
-        <v>1696</v>
+        <v>1902</v>
       </c>
       <c r="H379" t="s">
         <v>1137</v>
@@ -13302,7 +13313,7 @@
         <v>648</v>
       </c>
       <c r="G380" s="1" t="s">
-        <v>1698</v>
+        <v>1903</v>
       </c>
       <c r="H380" t="s">
         <v>1138</v>
@@ -13319,7 +13330,7 @@
         <v>648</v>
       </c>
       <c r="G381" s="1" t="s">
-        <v>1696</v>
+        <v>1904</v>
       </c>
       <c r="H381" t="s">
         <v>1139</v>
@@ -13336,7 +13347,7 @@
         <v>648</v>
       </c>
       <c r="G382" s="1" t="s">
-        <v>1696</v>
+        <v>1902</v>
       </c>
       <c r="H382" t="s">
         <v>1140</v>
@@ -13353,7 +13364,7 @@
         <v>648</v>
       </c>
       <c r="G383" s="1" t="s">
-        <v>1696</v>
+        <v>1904</v>
       </c>
       <c r="H383" t="s">
         <v>1141</v>
@@ -13370,7 +13381,7 @@
         <v>648</v>
       </c>
       <c r="G384" s="1" t="s">
-        <v>1696</v>
+        <v>1902</v>
       </c>
       <c r="H384" t="s">
         <v>1142</v>
@@ -13387,7 +13398,7 @@
         <v>648</v>
       </c>
       <c r="G385" s="1" t="s">
-        <v>1697</v>
+        <v>1905</v>
       </c>
       <c r="H385" t="s">
         <v>1143</v>
@@ -13404,7 +13415,7 @@
         <v>648</v>
       </c>
       <c r="G386" s="1" t="s">
-        <v>1696</v>
+        <v>1902</v>
       </c>
       <c r="H386" t="s">
         <v>1144</v>
@@ -13785,7 +13796,7 @@
         <v>687</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J9" s="26" t="s">
         <v>738</v>
@@ -13803,7 +13814,7 @@
         <v>687</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J10" s="26" t="s">
         <v>738</v>
@@ -13821,7 +13832,7 @@
         <v>687</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J11" s="26" t="s">
         <v>738</v>
@@ -13839,7 +13850,7 @@
         <v>687</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J12" s="26" t="s">
         <v>738</v>
@@ -13857,7 +13868,7 @@
         <v>687</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J13" s="26" t="s">
         <v>738</v>
@@ -13875,7 +13886,7 @@
         <v>687</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J14" s="26" t="s">
         <v>738</v>
@@ -13893,7 +13904,7 @@
         <v>687</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J15" s="26" t="s">
         <v>738</v>
@@ -13911,7 +13922,7 @@
         <v>687</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J16" s="26" t="s">
         <v>738</v>
@@ -13929,7 +13940,7 @@
         <v>687</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J17" s="26" t="s">
         <v>738</v>
@@ -13947,7 +13958,7 @@
         <v>687</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J18" s="26" t="s">
         <v>738</v>
@@ -13965,7 +13976,7 @@
         <v>687</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J19" s="26" t="s">
         <v>738</v>
@@ -13983,7 +13994,7 @@
         <v>687</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J20" s="26" t="s">
         <v>738</v>
@@ -14001,7 +14012,7 @@
         <v>687</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J21" s="26" t="s">
         <v>738</v>
@@ -14019,7 +14030,7 @@
         <v>687</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J22" s="26" t="s">
         <v>738</v>
@@ -14037,7 +14048,7 @@
         <v>687</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J23" s="26" t="s">
         <v>738</v>
@@ -14055,7 +14066,7 @@
         <v>687</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J24" s="26" t="s">
         <v>738</v>
@@ -14073,7 +14084,7 @@
         <v>687</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J25" s="26" t="s">
         <v>738</v>
@@ -14091,7 +14102,7 @@
         <v>687</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J26" s="26" t="s">
         <v>738</v>
@@ -14109,7 +14120,7 @@
         <v>687</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J27" s="26" t="s">
         <v>738</v>
@@ -14127,7 +14138,7 @@
         <v>687</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J28" s="26" t="s">
         <v>738</v>
@@ -14145,7 +14156,7 @@
         <v>687</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J29" s="26" t="s">
         <v>738</v>
@@ -14163,7 +14174,7 @@
         <v>687</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J30" s="26" t="s">
         <v>738</v>
@@ -14181,7 +14192,7 @@
         <v>687</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J31" s="26" t="s">
         <v>738</v>
@@ -14199,7 +14210,7 @@
         <v>687</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J32" s="26" t="s">
         <v>738</v>
@@ -14217,7 +14228,7 @@
         <v>687</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J33" s="26" t="s">
         <v>738</v>
@@ -14235,7 +14246,7 @@
         <v>687</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J34" s="26" t="s">
         <v>738</v>
@@ -14253,7 +14264,7 @@
         <v>687</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J35" s="26" t="s">
         <v>738</v>
@@ -14271,7 +14282,7 @@
         <v>687</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J36" s="26" t="s">
         <v>738</v>
@@ -14289,7 +14300,7 @@
         <v>687</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J37" s="26" t="s">
         <v>738</v>
@@ -14307,7 +14318,7 @@
         <v>687</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J38" s="26" t="s">
         <v>738</v>
@@ -14325,7 +14336,7 @@
         <v>687</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J39" s="26" t="s">
         <v>738</v>
@@ -14343,7 +14354,7 @@
         <v>687</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J40" s="26" t="s">
         <v>738</v>
@@ -14361,7 +14372,7 @@
         <v>687</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J41" s="26" t="s">
         <v>738</v>
@@ -14379,7 +14390,7 @@
         <v>687</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J42" s="26" t="s">
         <v>738</v>
@@ -14397,7 +14408,7 @@
         <v>687</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>1749</v>
+        <v>1744</v>
       </c>
       <c r="J43" s="26" t="s">
         <v>739</v>
@@ -14415,7 +14426,7 @@
         <v>687</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J44" s="26" t="s">
         <v>738</v>
@@ -14433,7 +14444,7 @@
         <v>687</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J45" s="26" t="s">
         <v>738</v>
@@ -14451,7 +14462,7 @@
         <v>687</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J46" s="26" t="s">
         <v>738</v>
@@ -14469,7 +14480,7 @@
         <v>687</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J47" s="26" t="s">
         <v>738</v>
@@ -14487,7 +14498,7 @@
         <v>687</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J48" s="26" t="s">
         <v>738</v>
@@ -14505,7 +14516,7 @@
         <v>687</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J49" s="26" t="s">
         <v>738</v>
@@ -14523,7 +14534,7 @@
         <v>687</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J50" s="26" t="s">
         <v>738</v>
@@ -14541,7 +14552,7 @@
         <v>687</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J51" s="26" t="s">
         <v>738</v>
@@ -14559,7 +14570,7 @@
         <v>687</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J52" s="26" t="s">
         <v>738</v>
@@ -14577,7 +14588,7 @@
         <v>687</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J53" s="26" t="s">
         <v>738</v>
@@ -14595,7 +14606,7 @@
         <v>687</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J54" s="26" t="s">
         <v>738</v>
@@ -14613,7 +14624,7 @@
         <v>687</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J55" s="26" t="s">
         <v>738</v>
@@ -14631,7 +14642,7 @@
         <v>687</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J56" s="26" t="s">
         <v>738</v>
@@ -14649,7 +14660,7 @@
         <v>687</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J57" s="26" t="s">
         <v>738</v>
@@ -14667,7 +14678,7 @@
         <v>687</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J58" s="26" t="s">
         <v>738</v>
@@ -14685,7 +14696,7 @@
         <v>687</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J59" s="26" t="s">
         <v>738</v>
@@ -14703,7 +14714,7 @@
         <v>687</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J60" s="26" t="s">
         <v>738</v>
@@ -14721,7 +14732,7 @@
         <v>687</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J61" s="26" t="s">
         <v>738</v>
@@ -14739,7 +14750,7 @@
         <v>687</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J62" s="26" t="s">
         <v>738</v>
@@ -14757,7 +14768,7 @@
         <v>687</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J63" s="26" t="s">
         <v>738</v>
@@ -14775,7 +14786,7 @@
         <v>687</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J64" s="1" t="s">
         <v>738</v>
@@ -14793,7 +14804,7 @@
         <v>687</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J65" s="26" t="s">
         <v>738</v>
@@ -14811,7 +14822,7 @@
         <v>687</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J66" s="26" t="s">
         <v>738</v>
@@ -14829,7 +14840,7 @@
         <v>687</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J67" s="26" t="s">
         <v>738</v>
@@ -14847,7 +14858,7 @@
         <v>687</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>1749</v>
+        <v>1744</v>
       </c>
       <c r="J68" s="26" t="s">
         <v>739</v>
@@ -14865,7 +14876,7 @@
         <v>687</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J69" s="1" t="s">
         <v>738</v>
@@ -14883,7 +14894,7 @@
         <v>687</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>1749</v>
+        <v>1744</v>
       </c>
       <c r="J70" s="26" t="s">
         <v>739</v>
@@ -14901,7 +14912,7 @@
         <v>687</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J71" s="1" t="s">
         <v>738</v>
@@ -14919,7 +14930,7 @@
         <v>687</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J72" s="1" t="s">
         <v>738</v>
@@ -14937,7 +14948,7 @@
         <v>687</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J73" s="1" t="s">
         <v>738</v>
@@ -14955,7 +14966,7 @@
         <v>687</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J74" s="1" t="s">
         <v>738</v>
@@ -14973,7 +14984,7 @@
         <v>687</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>1749</v>
+        <v>1744</v>
       </c>
       <c r="J75" s="26" t="s">
         <v>739</v>
@@ -14991,7 +15002,7 @@
         <v>687</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J76" s="1" t="s">
         <v>738</v>
@@ -15009,7 +15020,7 @@
         <v>687</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J77" s="1" t="s">
         <v>738</v>
@@ -15027,7 +15038,7 @@
         <v>687</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J78" s="1" t="s">
         <v>738</v>
@@ -15045,7 +15056,7 @@
         <v>687</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>738</v>
@@ -15063,7 +15074,7 @@
         <v>687</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J80" s="1" t="s">
         <v>738</v>
@@ -15081,7 +15092,7 @@
         <v>687</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J81" s="1" t="s">
         <v>738</v>
@@ -15099,7 +15110,7 @@
         <v>687</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J82" s="1" t="s">
         <v>738</v>
@@ -15117,7 +15128,7 @@
         <v>687</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J83" s="1" t="s">
         <v>738</v>
@@ -15135,7 +15146,7 @@
         <v>687</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J84" s="1" t="s">
         <v>738</v>
@@ -15153,7 +15164,7 @@
         <v>687</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J85" s="1" t="s">
         <v>738</v>
@@ -15171,7 +15182,7 @@
         <v>687</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J86" s="1" t="s">
         <v>738</v>
@@ -15189,7 +15200,7 @@
         <v>687</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J87" s="1" t="s">
         <v>738</v>
@@ -15207,7 +15218,7 @@
         <v>687</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J88" s="1" t="s">
         <v>738</v>
@@ -15225,7 +15236,7 @@
         <v>687</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J89" s="1" t="s">
         <v>738</v>
@@ -15243,7 +15254,7 @@
         <v>687</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J90" s="1" t="s">
         <v>738</v>
@@ -15261,7 +15272,7 @@
         <v>687</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>1749</v>
+        <v>1744</v>
       </c>
       <c r="J91" s="26" t="s">
         <v>739</v>
@@ -15279,7 +15290,7 @@
         <v>687</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J92" s="1" t="s">
         <v>738</v>
@@ -15297,7 +15308,7 @@
         <v>687</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J93" s="1" t="s">
         <v>738</v>
@@ -15315,7 +15326,7 @@
         <v>687</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>1750</v>
+        <v>1745</v>
       </c>
       <c r="J94" s="26" t="s">
         <v>740</v>
@@ -15333,7 +15344,7 @@
         <v>687</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J95" s="1" t="s">
         <v>738</v>
@@ -15351,7 +15362,7 @@
         <v>687</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J96" s="1" t="s">
         <v>738</v>
@@ -15369,7 +15380,7 @@
         <v>687</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>1749</v>
+        <v>1744</v>
       </c>
       <c r="J97" s="26" t="s">
         <v>739</v>
@@ -15387,7 +15398,7 @@
         <v>687</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>1749</v>
+        <v>1744</v>
       </c>
       <c r="J98" s="26" t="s">
         <v>739</v>
@@ -15405,7 +15416,7 @@
         <v>687</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J99" s="1" t="s">
         <v>738</v>
@@ -15423,7 +15434,7 @@
         <v>687</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J100" s="1" t="s">
         <v>738</v>
@@ -15441,7 +15452,7 @@
         <v>687</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J101" s="1" t="s">
         <v>738</v>
@@ -15459,7 +15470,7 @@
         <v>687</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J102" s="1" t="s">
         <v>738</v>
@@ -15477,7 +15488,7 @@
         <v>687</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J103" s="1" t="s">
         <v>738</v>
@@ -15495,7 +15506,7 @@
         <v>687</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J104" s="1" t="s">
         <v>738</v>
@@ -15513,7 +15524,7 @@
         <v>687</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>1750</v>
+        <v>1745</v>
       </c>
       <c r="J105" s="26" t="s">
         <v>740</v>
@@ -15531,7 +15542,7 @@
         <v>687</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J106" s="1" t="s">
         <v>738</v>
@@ -15549,7 +15560,7 @@
         <v>687</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J107" s="1" t="s">
         <v>738</v>
@@ -15567,7 +15578,7 @@
         <v>687</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J108" s="1" t="s">
         <v>738</v>
@@ -15585,7 +15596,7 @@
         <v>687</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J109" s="1" t="s">
         <v>738</v>
@@ -15603,7 +15614,7 @@
         <v>687</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J110" s="1" t="s">
         <v>738</v>
@@ -15621,7 +15632,7 @@
         <v>687</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J111" s="1" t="s">
         <v>738</v>
@@ -15639,7 +15650,7 @@
         <v>687</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J112" s="1" t="s">
         <v>738</v>
@@ -15657,7 +15668,7 @@
         <v>687</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>1749</v>
+        <v>1744</v>
       </c>
       <c r="J113" s="26" t="s">
         <v>739</v>
@@ -15675,7 +15686,7 @@
         <v>687</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J114" s="1" t="s">
         <v>738</v>
@@ -15693,7 +15704,7 @@
         <v>687</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J115" s="1" t="s">
         <v>738</v>
@@ -15711,7 +15722,7 @@
         <v>687</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J116" s="1" t="s">
         <v>738</v>
@@ -15729,7 +15740,7 @@
         <v>687</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J117" s="1" t="s">
         <v>738</v>
@@ -15747,7 +15758,7 @@
         <v>687</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J118" s="1" t="s">
         <v>738</v>
@@ -15765,7 +15776,7 @@
         <v>687</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>1749</v>
+        <v>1744</v>
       </c>
       <c r="J119" s="26" t="s">
         <v>739</v>
@@ -15783,7 +15794,7 @@
         <v>687</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J120" s="1" t="s">
         <v>738</v>
@@ -15801,7 +15812,7 @@
         <v>687</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J121" s="1" t="s">
         <v>738</v>
@@ -15819,7 +15830,7 @@
         <v>687</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J122" s="1" t="s">
         <v>738</v>
@@ -15837,7 +15848,7 @@
         <v>687</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J123" s="1" t="s">
         <v>738</v>
@@ -15855,7 +15866,7 @@
         <v>687</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J124" s="1" t="s">
         <v>738</v>
@@ -15873,7 +15884,7 @@
         <v>687</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J125" s="1" t="s">
         <v>738</v>
@@ -15891,7 +15902,7 @@
         <v>687</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J126" s="1" t="s">
         <v>738</v>
@@ -15909,7 +15920,7 @@
         <v>687</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J127" s="1" t="s">
         <v>738</v>
@@ -15927,7 +15938,7 @@
         <v>687</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J128" s="1" t="s">
         <v>738</v>
@@ -15945,7 +15956,7 @@
         <v>687</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J129" s="1" t="s">
         <v>738</v>
@@ -15963,7 +15974,7 @@
         <v>687</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J130" s="1" t="s">
         <v>738</v>
@@ -15981,7 +15992,7 @@
         <v>687</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J131" s="1" t="s">
         <v>738</v>
@@ -15999,7 +16010,7 @@
         <v>687</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J132" s="1" t="s">
         <v>738</v>
@@ -16017,7 +16028,7 @@
         <v>687</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J133" s="1" t="s">
         <v>738</v>
@@ -16035,7 +16046,7 @@
         <v>687</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J134" s="1" t="s">
         <v>738</v>
@@ -16053,7 +16064,7 @@
         <v>687</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J135" s="1" t="s">
         <v>738</v>
@@ -16071,7 +16082,7 @@
         <v>687</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J136" s="1" t="s">
         <v>738</v>
@@ -16089,7 +16100,7 @@
         <v>687</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>1749</v>
+        <v>1744</v>
       </c>
       <c r="J137" s="26" t="s">
         <v>739</v>
@@ -16107,7 +16118,7 @@
         <v>687</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>1749</v>
+        <v>1744</v>
       </c>
       <c r="J138" s="26" t="s">
         <v>739</v>
@@ -16125,7 +16136,7 @@
         <v>687</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J139" s="1" t="s">
         <v>738</v>
@@ -16143,7 +16154,7 @@
         <v>687</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J140" s="1" t="s">
         <v>738</v>
@@ -16161,7 +16172,7 @@
         <v>687</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J141" s="1" t="s">
         <v>738</v>
@@ -16179,7 +16190,7 @@
         <v>687</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J142" s="1" t="s">
         <v>738</v>
@@ -16197,7 +16208,7 @@
         <v>687</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J143" s="1" t="s">
         <v>738</v>
@@ -16215,7 +16226,7 @@
         <v>687</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J144" s="1" t="s">
         <v>738</v>
@@ -16233,7 +16244,7 @@
         <v>687</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J145" s="1" t="s">
         <v>738</v>
@@ -16251,7 +16262,7 @@
         <v>687</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J146" s="1" t="s">
         <v>738</v>
@@ -16269,7 +16280,7 @@
         <v>687</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J147" s="1" t="s">
         <v>738</v>
@@ -16287,7 +16298,7 @@
         <v>687</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J148" s="1" t="s">
         <v>738</v>
@@ -16305,7 +16316,7 @@
         <v>687</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J149" s="1" t="s">
         <v>738</v>
@@ -16323,7 +16334,7 @@
         <v>687</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J150" s="1" t="s">
         <v>738</v>
@@ -16341,7 +16352,7 @@
         <v>687</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J151" s="1" t="s">
         <v>738</v>
@@ -16359,7 +16370,7 @@
         <v>687</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J152" s="1" t="s">
         <v>738</v>
@@ -16377,7 +16388,7 @@
         <v>687</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J153" s="1" t="s">
         <v>738</v>
@@ -16395,7 +16406,7 @@
         <v>687</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J154" s="1" t="s">
         <v>738</v>
@@ -16413,7 +16424,7 @@
         <v>687</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J155" s="1" t="s">
         <v>738</v>
@@ -16431,7 +16442,7 @@
         <v>687</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J156" s="1" t="s">
         <v>738</v>
@@ -16449,7 +16460,7 @@
         <v>687</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J157" s="1" t="s">
         <v>738</v>
@@ -16467,7 +16478,7 @@
         <v>687</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J158" s="1" t="s">
         <v>738</v>
@@ -16485,7 +16496,7 @@
         <v>687</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J159" s="1" t="s">
         <v>738</v>
@@ -16503,7 +16514,7 @@
         <v>687</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J160" s="1" t="s">
         <v>738</v>
@@ -16521,7 +16532,7 @@
         <v>687</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J161" s="1" t="s">
         <v>738</v>
@@ -16539,7 +16550,7 @@
         <v>687</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J162" s="1" t="s">
         <v>738</v>
@@ -16557,7 +16568,7 @@
         <v>687</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J163" s="1" t="s">
         <v>738</v>
@@ -16575,7 +16586,7 @@
         <v>687</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J164" s="1" t="s">
         <v>738</v>
@@ -16593,7 +16604,7 @@
         <v>687</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J165" s="1" t="s">
         <v>738</v>
@@ -16611,7 +16622,7 @@
         <v>687</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="J166" s="1" t="s">
         <v>738</v>
@@ -16630,7 +16641,7 @@
         <v>687</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>1855</v>
+        <v>1846</v>
       </c>
       <c r="K167" t="s">
         <v>1305</v>
@@ -16646,7 +16657,7 @@
         <v>687</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>1856</v>
+        <v>1847</v>
       </c>
       <c r="K168" t="s">
         <v>1306</v>
@@ -16662,7 +16673,7 @@
         <v>687</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>1857</v>
+        <v>1848</v>
       </c>
       <c r="K169" t="s">
         <v>1307</v>
@@ -16678,7 +16689,7 @@
         <v>687</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>1858</v>
+        <v>1849</v>
       </c>
       <c r="K170" t="s">
         <v>1308</v>
@@ -16694,7 +16705,7 @@
         <v>687</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>1859</v>
+        <v>1850</v>
       </c>
       <c r="J171" s="1" t="s">
         <v>1694</v>
@@ -16713,7 +16724,7 @@
         <v>687</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>1860</v>
+        <v>1851</v>
       </c>
       <c r="K172" t="s">
         <v>1309</v>
@@ -16728,7 +16739,7 @@
         <v>687</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>1861</v>
+        <v>1852</v>
       </c>
       <c r="K173" t="s">
         <v>1310</v>
@@ -16743,7 +16754,7 @@
         <v>741</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>1862</v>
+        <v>1853</v>
       </c>
       <c r="K174" t="s">
         <v>1311</v>
@@ -16759,7 +16770,7 @@
         <v>687</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>1863</v>
+        <v>1854</v>
       </c>
       <c r="K175" t="s">
         <v>1312</v>
@@ -16775,7 +16786,7 @@
         <v>687</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>1864</v>
+        <v>1855</v>
       </c>
       <c r="K176" t="s">
         <v>1313</v>
@@ -16792,7 +16803,7 @@
       <c r="G177" s="1"/>
       <c r="H177" s="1"/>
       <c r="I177" s="1" t="s">
-        <v>1865</v>
+        <v>1856</v>
       </c>
       <c r="K177" t="s">
         <v>1314</v>
@@ -16807,7 +16818,7 @@
         <v>687</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>1866</v>
+        <v>1857</v>
       </c>
       <c r="K178" t="s">
         <v>1315</v>
@@ -16822,7 +16833,7 @@
         <v>687</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>1867</v>
+        <v>1858</v>
       </c>
       <c r="K179" t="s">
         <v>1316</v>
@@ -16837,7 +16848,7 @@
         <v>687</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>1868</v>
+        <v>1859</v>
       </c>
       <c r="K180" t="s">
         <v>1317</v>
@@ -16853,7 +16864,7 @@
         <v>687</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>1869</v>
+        <v>1860</v>
       </c>
       <c r="K181" t="s">
         <v>1318</v>
@@ -17143,7 +17154,7 @@
         <v>687</v>
       </c>
       <c r="I202" s="9" t="s">
-        <v>1870</v>
+        <v>1861</v>
       </c>
       <c r="J202" s="1" t="s">
         <v>744</v>
@@ -17162,7 +17173,7 @@
         <v>687</v>
       </c>
       <c r="I203" s="9" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="K203" t="s">
         <v>1506</v>
@@ -17178,7 +17189,7 @@
         <v>741</v>
       </c>
       <c r="I204" s="9" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="K204" t="s">
         <v>1507</v>
@@ -17192,7 +17203,7 @@
         <v>741</v>
       </c>
       <c r="I205" s="1" t="s">
-        <v>1753</v>
+        <v>1748</v>
       </c>
       <c r="K205" t="s">
         <v>1487</v>
@@ -17206,7 +17217,7 @@
         <v>687</v>
       </c>
       <c r="I206" s="9" t="s">
-        <v>1870</v>
+        <v>1861</v>
       </c>
       <c r="J206" s="1" t="s">
         <v>744</v>
@@ -17227,7 +17238,7 @@
       <c r="G207" s="1"/>
       <c r="H207" s="1"/>
       <c r="I207" s="9" t="s">
-        <v>1871</v>
+        <v>1862</v>
       </c>
       <c r="J207" s="40" t="s">
         <v>746</v>
@@ -17244,7 +17255,7 @@
         <v>687</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>1872</v>
+        <v>1863</v>
       </c>
       <c r="K208" t="s">
         <v>1342</v>
@@ -17258,7 +17269,7 @@
         <v>687</v>
       </c>
       <c r="I209" s="1" t="s">
-        <v>1873</v>
+        <v>1864</v>
       </c>
       <c r="J209" s="1" t="s">
         <v>747</v>
@@ -17277,7 +17288,7 @@
         <v>687</v>
       </c>
       <c r="I210" s="9" t="s">
-        <v>1754</v>
+        <v>1749</v>
       </c>
       <c r="J210" s="1" t="s">
         <v>748</v>
@@ -17296,7 +17307,7 @@
         <v>741</v>
       </c>
       <c r="I211" s="9" t="s">
-        <v>1755</v>
+        <v>1750</v>
       </c>
       <c r="K211" t="s">
         <v>1526</v>
@@ -17310,7 +17321,7 @@
         <v>687</v>
       </c>
       <c r="I212" s="1" t="s">
-        <v>1756</v>
+        <v>1751</v>
       </c>
       <c r="K212" t="s">
         <v>1344</v>
@@ -17324,7 +17335,7 @@
         <v>741</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>1757</v>
+        <v>1752</v>
       </c>
       <c r="K213" t="s">
         <v>1488</v>
@@ -17338,7 +17349,7 @@
         <v>687</v>
       </c>
       <c r="I214" s="1" t="s">
-        <v>1758</v>
+        <v>1753</v>
       </c>
       <c r="J214" s="1" t="s">
         <v>749</v>
@@ -17355,7 +17366,7 @@
         <v>687</v>
       </c>
       <c r="I215" s="1" t="s">
-        <v>1874</v>
+        <v>1865</v>
       </c>
       <c r="J215" s="1" t="s">
         <v>750</v>
@@ -17374,7 +17385,7 @@
         <v>687</v>
       </c>
       <c r="I216" s="9" t="s">
-        <v>1759</v>
+        <v>1754</v>
       </c>
       <c r="K216" t="s">
         <v>1502</v>
@@ -17390,7 +17401,7 @@
         <v>741</v>
       </c>
       <c r="I217" s="9" t="s">
-        <v>1760</v>
+        <v>1755</v>
       </c>
       <c r="K217" t="s">
         <v>1503</v>
@@ -17404,7 +17415,7 @@
         <v>687</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>1761</v>
+        <v>1756</v>
       </c>
       <c r="K218" t="s">
         <v>1512</v>
@@ -17418,7 +17429,7 @@
         <v>741</v>
       </c>
       <c r="I219" s="1" t="s">
-        <v>1762</v>
+        <v>1757</v>
       </c>
       <c r="K219" s="53" t="s">
         <v>1513</v>
@@ -17434,7 +17445,7 @@
         <v>687</v>
       </c>
       <c r="I220" s="9" t="s">
-        <v>1763</v>
+        <v>1758</v>
       </c>
       <c r="J220" s="1" t="s">
         <v>751</v>
@@ -17453,7 +17464,7 @@
         <v>741</v>
       </c>
       <c r="I221" s="9" t="s">
-        <v>1764</v>
+        <v>1759</v>
       </c>
       <c r="K221" t="s">
         <v>1538</v>
@@ -17469,7 +17480,7 @@
         <v>687</v>
       </c>
       <c r="I222" s="9" t="s">
-        <v>1763</v>
+        <v>1758</v>
       </c>
       <c r="J222" s="1" t="s">
         <v>751</v>
@@ -17488,7 +17499,7 @@
         <v>741</v>
       </c>
       <c r="I223" s="9" t="s">
-        <v>1764</v>
+        <v>1759</v>
       </c>
       <c r="K223" t="s">
         <v>1493</v>
@@ -17502,7 +17513,7 @@
         <v>687</v>
       </c>
       <c r="I224" s="1" t="s">
-        <v>1765</v>
+        <v>1760</v>
       </c>
       <c r="K224" t="s">
         <v>1494</v>
@@ -17516,7 +17527,7 @@
         <v>741</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>1766</v>
+        <v>1761</v>
       </c>
       <c r="K225" t="s">
         <v>1495</v>
@@ -17532,7 +17543,7 @@
         <v>687</v>
       </c>
       <c r="I226" s="9" t="s">
-        <v>1759</v>
+        <v>1754</v>
       </c>
       <c r="K226" s="53" t="s">
         <v>1500</v>
@@ -17548,7 +17559,7 @@
         <v>741</v>
       </c>
       <c r="I227" s="9" t="s">
-        <v>1760</v>
+        <v>1755</v>
       </c>
       <c r="K227" t="s">
         <v>1501</v>
@@ -17562,7 +17573,7 @@
         <v>687</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>1767</v>
+        <v>1762</v>
       </c>
       <c r="J228" s="1" t="s">
         <v>752</v>
@@ -17579,7 +17590,7 @@
         <v>687</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>1768</v>
+        <v>1763</v>
       </c>
       <c r="J229" s="1" t="s">
         <v>753</v>
@@ -17598,7 +17609,7 @@
         <v>687</v>
       </c>
       <c r="I230" s="9" t="s">
-        <v>1751</v>
+        <v>1746</v>
       </c>
       <c r="K230" t="s">
         <v>1504</v>
@@ -17614,7 +17625,7 @@
         <v>741</v>
       </c>
       <c r="I231" s="9" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="K231" t="s">
         <v>1505</v>
@@ -17628,7 +17639,7 @@
         <v>687</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>1875</v>
+        <v>1866</v>
       </c>
       <c r="J232" s="1" t="s">
         <v>754</v>
@@ -17645,7 +17656,7 @@
         <v>687</v>
       </c>
       <c r="I233" s="1" t="s">
-        <v>1876</v>
+        <v>1867</v>
       </c>
       <c r="J233" s="1" t="s">
         <v>755</v>
@@ -17662,7 +17673,7 @@
         <v>687</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>1769</v>
+        <v>1764</v>
       </c>
       <c r="J234" s="1" t="s">
         <v>678</v>
@@ -17679,7 +17690,7 @@
         <v>687</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>1761</v>
+        <v>1756</v>
       </c>
       <c r="K235" t="s">
         <v>1508</v>
@@ -17693,7 +17704,7 @@
         <v>741</v>
       </c>
       <c r="I236" s="1" t="s">
-        <v>1762</v>
+        <v>1757</v>
       </c>
       <c r="K236" t="s">
         <v>1509</v>
@@ -17707,7 +17718,7 @@
         <v>687</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>1769</v>
+        <v>1764</v>
       </c>
       <c r="J237" s="1" t="s">
         <v>678</v>
@@ -17726,7 +17737,7 @@
         <v>687</v>
       </c>
       <c r="I238" s="9" t="s">
-        <v>1763</v>
+        <v>1758</v>
       </c>
       <c r="J238" s="1" t="s">
         <v>751</v>
@@ -17745,7 +17756,7 @@
         <v>741</v>
       </c>
       <c r="I239" s="9" t="s">
-        <v>1764</v>
+        <v>1759</v>
       </c>
       <c r="K239" t="s">
         <v>1491</v>
@@ -17759,7 +17770,7 @@
         <v>687</v>
       </c>
       <c r="I240" s="1" t="s">
-        <v>1770</v>
+        <v>1765</v>
       </c>
       <c r="K240" t="s">
         <v>1353</v>
@@ -17773,7 +17784,7 @@
         <v>687</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>1877</v>
+        <v>1868</v>
       </c>
       <c r="J241" s="1" t="s">
         <v>756</v>
@@ -17792,10 +17803,10 @@
         <v>741</v>
       </c>
       <c r="I242" s="9" t="s">
-        <v>1878</v>
+        <v>1869</v>
       </c>
       <c r="K242" t="s">
-        <v>1710</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="243" spans="1:11">
@@ -17808,7 +17819,7 @@
         <v>687</v>
       </c>
       <c r="I243" s="9" t="s">
-        <v>1771</v>
+        <v>1766</v>
       </c>
       <c r="J243" s="1" t="s">
         <v>757</v>
@@ -17827,7 +17838,7 @@
         <v>741</v>
       </c>
       <c r="I244" s="9" t="s">
-        <v>1772</v>
+        <v>1767</v>
       </c>
       <c r="K244" t="s">
         <v>1356</v>
@@ -17841,7 +17852,7 @@
         <v>741</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>1773</v>
+        <v>1768</v>
       </c>
       <c r="K245" t="s">
         <v>1514</v>
@@ -17855,7 +17866,7 @@
         <v>687</v>
       </c>
       <c r="I246" s="1" t="s">
-        <v>1774</v>
+        <v>1769</v>
       </c>
       <c r="K246" t="s">
         <v>1357</v>
@@ -17869,7 +17880,7 @@
         <v>687</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>1774</v>
+        <v>1769</v>
       </c>
       <c r="K247" t="s">
         <v>1358</v>
@@ -17883,7 +17894,7 @@
         <v>687</v>
       </c>
       <c r="I248" s="1" t="s">
-        <v>1775</v>
+        <v>1770</v>
       </c>
       <c r="K248" t="s">
         <v>1359</v>
@@ -17899,7 +17910,7 @@
         <v>687</v>
       </c>
       <c r="I249" s="9" t="s">
-        <v>1771</v>
+        <v>1766</v>
       </c>
       <c r="J249" s="1" t="s">
         <v>757</v>
@@ -17918,7 +17929,7 @@
         <v>741</v>
       </c>
       <c r="I250" s="9" t="s">
-        <v>1772</v>
+        <v>1767</v>
       </c>
       <c r="K250" t="s">
         <v>1361</v>
@@ -17932,7 +17943,7 @@
         <v>687</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>1769</v>
+        <v>1764</v>
       </c>
       <c r="J251" s="1" t="s">
         <v>678</v>
@@ -17949,7 +17960,7 @@
         <v>687</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>1769</v>
+        <v>1764</v>
       </c>
       <c r="J252" s="1" t="s">
         <v>678</v>
@@ -17966,7 +17977,7 @@
         <v>687</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>1769</v>
+        <v>1764</v>
       </c>
       <c r="J253" s="1" t="s">
         <v>678</v>
@@ -17983,7 +17994,7 @@
         <v>687</v>
       </c>
       <c r="I254" s="1" t="s">
-        <v>1769</v>
+        <v>1764</v>
       </c>
       <c r="J254" s="1" t="s">
         <v>678</v>
@@ -18000,7 +18011,7 @@
         <v>687</v>
       </c>
       <c r="I255" s="1" t="s">
-        <v>1761</v>
+        <v>1756</v>
       </c>
       <c r="K255" t="s">
         <v>1510</v>
@@ -18014,7 +18025,7 @@
         <v>741</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>1762</v>
+        <v>1757</v>
       </c>
       <c r="K256" t="s">
         <v>1511</v>
@@ -18028,7 +18039,7 @@
         <v>741</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>1776</v>
+        <v>1771</v>
       </c>
       <c r="K257" t="s">
         <v>1366</v>
@@ -18042,7 +18053,7 @@
         <v>687</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>1756</v>
+        <v>1751</v>
       </c>
       <c r="K258" t="s">
         <v>1367</v>
@@ -18056,7 +18067,7 @@
         <v>741</v>
       </c>
       <c r="I259" s="1" t="s">
-        <v>1757</v>
+        <v>1752</v>
       </c>
       <c r="K259" t="s">
         <v>1489</v>
@@ -18070,7 +18081,7 @@
         <v>687</v>
       </c>
       <c r="I260" s="1" t="s">
-        <v>1777</v>
+        <v>1772</v>
       </c>
       <c r="K260" t="s">
         <v>1368</v>
@@ -18084,7 +18095,7 @@
         <v>741</v>
       </c>
       <c r="I261" s="1" t="s">
-        <v>1778</v>
+        <v>1773</v>
       </c>
       <c r="K261" t="s">
         <v>1515</v>
@@ -18100,7 +18111,7 @@
         <v>687</v>
       </c>
       <c r="I262" s="9" t="s">
-        <v>1779</v>
+        <v>1774</v>
       </c>
       <c r="K262" t="s">
         <v>1516</v>
@@ -18116,7 +18127,7 @@
         <v>741</v>
       </c>
       <c r="I263" s="9" t="s">
-        <v>1780</v>
+        <v>1775</v>
       </c>
       <c r="K263" s="53" t="s">
         <v>1517</v>
@@ -18130,7 +18141,7 @@
         <v>687</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>1781</v>
+        <v>1776</v>
       </c>
       <c r="K264" t="s">
         <v>1369</v>
@@ -18144,7 +18155,7 @@
         <v>741</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>1782</v>
+        <v>1777</v>
       </c>
       <c r="K265" t="s">
         <v>1518</v>
@@ -18158,7 +18169,7 @@
         <v>741</v>
       </c>
       <c r="I266" s="1" t="s">
-        <v>1783</v>
+        <v>1778</v>
       </c>
       <c r="K266" t="s">
         <v>1519</v>
@@ -18172,7 +18183,7 @@
         <v>687</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>1781</v>
+        <v>1776</v>
       </c>
       <c r="K267" t="s">
         <v>1520</v>
@@ -18186,7 +18197,7 @@
         <v>741</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>1782</v>
+        <v>1777</v>
       </c>
       <c r="K268" t="s">
         <v>1521</v>
@@ -18202,7 +18213,7 @@
         <v>687</v>
       </c>
       <c r="I269" s="9" t="s">
-        <v>1754</v>
+        <v>1749</v>
       </c>
       <c r="J269" s="1" t="s">
         <v>748</v>
@@ -18221,7 +18232,7 @@
         <v>741</v>
       </c>
       <c r="I270" s="9" t="s">
-        <v>1755</v>
+        <v>1750</v>
       </c>
       <c r="K270" t="s">
         <v>1528</v>
@@ -18237,7 +18248,7 @@
         <v>687</v>
       </c>
       <c r="I271" s="9" t="s">
-        <v>1771</v>
+        <v>1766</v>
       </c>
       <c r="J271" s="1" t="s">
         <v>757</v>
@@ -18256,7 +18267,7 @@
         <v>741</v>
       </c>
       <c r="I272" s="9" t="s">
-        <v>1772</v>
+        <v>1767</v>
       </c>
       <c r="K272" t="s">
         <v>1371</v>
@@ -18272,7 +18283,7 @@
         <v>687</v>
       </c>
       <c r="I273" s="9" t="s">
-        <v>1879</v>
+        <v>1870</v>
       </c>
       <c r="K273" t="s">
         <v>1372</v>
@@ -18286,7 +18297,7 @@
         <v>687</v>
       </c>
       <c r="I274" s="1" t="s">
-        <v>1774</v>
+        <v>1769</v>
       </c>
       <c r="K274" t="s">
         <v>1373</v>
@@ -18300,7 +18311,7 @@
         <v>687</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>1768</v>
+        <v>1763</v>
       </c>
       <c r="K275" t="s">
         <v>1374</v>
@@ -18314,7 +18325,7 @@
         <v>687</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>1880</v>
+        <v>1871</v>
       </c>
       <c r="K276" t="s">
         <v>1375</v>
@@ -18328,7 +18339,7 @@
         <v>687</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>1784</v>
+        <v>1779</v>
       </c>
       <c r="J277" s="1" t="s">
         <v>758</v>
@@ -18345,7 +18356,7 @@
         <v>687</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>1880</v>
+        <v>1871</v>
       </c>
       <c r="K278" t="s">
         <v>1377</v>
@@ -18359,7 +18370,7 @@
         <v>687</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>1881</v>
+        <v>1872</v>
       </c>
       <c r="K279" t="s">
         <v>1378</v>
@@ -18373,7 +18384,7 @@
         <v>687</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>1785</v>
+        <v>1780</v>
       </c>
       <c r="J280" s="1" t="s">
         <v>727</v>
@@ -18390,7 +18401,7 @@
         <v>687</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>1786</v>
+        <v>1781</v>
       </c>
       <c r="K281" t="s">
         <v>1380</v>
@@ -18404,7 +18415,7 @@
         <v>687</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>1787</v>
+        <v>1782</v>
       </c>
       <c r="K282" t="s">
         <v>1381</v>
@@ -18418,7 +18429,7 @@
         <v>741</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>1788</v>
+        <v>1783</v>
       </c>
       <c r="K283" t="s">
         <v>1522</v>
@@ -18432,7 +18443,7 @@
         <v>741</v>
       </c>
       <c r="I284" s="1" t="s">
-        <v>1789</v>
+        <v>1784</v>
       </c>
       <c r="K284" t="s">
         <v>1382</v>
@@ -18448,7 +18459,7 @@
         <v>687</v>
       </c>
       <c r="I285" s="9" t="s">
-        <v>1771</v>
+        <v>1766</v>
       </c>
       <c r="J285" s="1" t="s">
         <v>757</v>
@@ -18467,7 +18478,7 @@
         <v>741</v>
       </c>
       <c r="I286" s="9" t="s">
-        <v>1772</v>
+        <v>1767</v>
       </c>
       <c r="K286" t="s">
         <v>1384</v>
@@ -18481,7 +18492,7 @@
         <v>687</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>1765</v>
+        <v>1760</v>
       </c>
       <c r="K287" t="s">
         <v>1496</v>
@@ -18495,7 +18506,7 @@
         <v>741</v>
       </c>
       <c r="I288" s="1" t="s">
-        <v>1766</v>
+        <v>1761</v>
       </c>
       <c r="K288" t="s">
         <v>1497</v>
@@ -18509,7 +18520,7 @@
         <v>687</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>1765</v>
+        <v>1760</v>
       </c>
       <c r="K289" t="s">
         <v>1498</v>
@@ -18523,7 +18534,7 @@
         <v>741</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>1766</v>
+        <v>1761</v>
       </c>
       <c r="K290" t="s">
         <v>1499</v>
@@ -18539,13 +18550,13 @@
       </c>
       <c r="H291"/>
       <c r="I291" s="1" t="s">
-        <v>1790</v>
+        <v>1785</v>
       </c>
       <c r="J291" s="26" t="s">
-        <v>1733</v>
+        <v>1728</v>
       </c>
       <c r="K291" s="1" t="s">
-        <v>1730</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="292" spans="1:11" ht="72">
@@ -18558,13 +18569,13 @@
       </c>
       <c r="H292"/>
       <c r="I292" s="1" t="s">
-        <v>1790</v>
+        <v>1785</v>
       </c>
       <c r="J292" s="26" t="s">
-        <v>1733</v>
+        <v>1728</v>
       </c>
       <c r="K292" s="1" t="s">
-        <v>1731</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="293" spans="1:11" ht="72">
@@ -18577,13 +18588,13 @@
       </c>
       <c r="H293"/>
       <c r="I293" s="1" t="s">
-        <v>1790</v>
+        <v>1785</v>
       </c>
       <c r="J293" s="26" t="s">
-        <v>1733</v>
+        <v>1728</v>
       </c>
       <c r="K293" s="1" t="s">
-        <v>1732</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="294" spans="1:11" ht="57.6">
@@ -18596,13 +18607,13 @@
       </c>
       <c r="H294"/>
       <c r="I294" s="1" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="J294" s="26" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="K294" s="1" t="s">
-        <v>1711</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="295" spans="1:11" ht="57.6">
@@ -18615,13 +18626,13 @@
       </c>
       <c r="H295"/>
       <c r="I295" s="1" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="J295" s="26" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="K295" s="1" t="s">
-        <v>1712</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="296" spans="1:11" ht="57.6">
@@ -18634,13 +18645,13 @@
       </c>
       <c r="H296"/>
       <c r="I296" s="1" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="J296" s="26" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="K296" s="1" t="s">
-        <v>1713</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="297" spans="1:11" ht="57.6">
@@ -18653,13 +18664,13 @@
       </c>
       <c r="H297"/>
       <c r="I297" s="1" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="J297" s="26" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="K297" s="54" t="s">
-        <v>1714</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="298" spans="1:11" ht="57.6">
@@ -18672,13 +18683,13 @@
       </c>
       <c r="H298"/>
       <c r="I298" s="1" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="J298" s="26" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="K298" s="1" t="s">
-        <v>1715</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="299" spans="1:11" ht="57.6">
@@ -18691,13 +18702,13 @@
       </c>
       <c r="H299"/>
       <c r="I299" s="1" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="J299" s="26" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="K299" s="1" t="s">
-        <v>1716</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="300" spans="1:11" ht="57.6">
@@ -18710,13 +18721,13 @@
       </c>
       <c r="H300"/>
       <c r="I300" s="1" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="J300" s="26" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="K300" s="1" t="s">
-        <v>1717</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="301" spans="1:11" ht="57.6">
@@ -18729,13 +18740,13 @@
       </c>
       <c r="H301"/>
       <c r="I301" s="1" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="J301" s="26" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="K301" s="1" t="s">
-        <v>1718</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="302" spans="1:11" ht="57.6">
@@ -18748,13 +18759,13 @@
       </c>
       <c r="H302"/>
       <c r="I302" s="1" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="J302" s="26" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="K302" s="1" t="s">
-        <v>1719</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="303" spans="1:11" ht="57.6">
@@ -18767,13 +18778,13 @@
       </c>
       <c r="H303"/>
       <c r="I303" s="1" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="J303" s="26" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="K303" s="1" t="s">
-        <v>1720</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="304" spans="1:11" ht="57.6">
@@ -18786,13 +18797,13 @@
       </c>
       <c r="H304"/>
       <c r="I304" s="1" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="J304" s="26" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="K304" s="1" t="s">
-        <v>1721</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="305" spans="1:11" ht="57.6">
@@ -18805,13 +18816,13 @@
       </c>
       <c r="H305"/>
       <c r="I305" s="1" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="J305" s="26" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="K305" s="1" t="s">
-        <v>1722</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="306" spans="1:11" ht="57.6">
@@ -18824,13 +18835,13 @@
       </c>
       <c r="H306"/>
       <c r="I306" s="1" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="J306" s="26" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="K306" s="1" t="s">
-        <v>1723</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="307" spans="1:11" ht="57.6">
@@ -18843,13 +18854,13 @@
       </c>
       <c r="H307"/>
       <c r="I307" s="1" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="J307" s="26" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="K307" s="1" t="s">
-        <v>1724</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="308" spans="1:11" ht="57.6">
@@ -18862,13 +18873,13 @@
       </c>
       <c r="H308"/>
       <c r="I308" s="1" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="J308" s="26" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="K308" s="1" t="s">
-        <v>1725</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="309" spans="1:11" ht="57.6">
@@ -18881,13 +18892,13 @@
       </c>
       <c r="H309"/>
       <c r="I309" s="1" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="J309" s="26" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="K309" s="1" t="s">
-        <v>1726</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="310" spans="1:11" ht="57.6">
@@ -18900,13 +18911,13 @@
       </c>
       <c r="H310"/>
       <c r="I310" s="1" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="J310" s="26" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="K310" s="1" t="s">
-        <v>1727</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="311" spans="1:11" ht="57.6">
@@ -18919,13 +18930,13 @@
       </c>
       <c r="H311"/>
       <c r="I311" s="1" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="J311" s="26" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="K311" s="1" t="s">
-        <v>1728</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="312" spans="1:11" ht="57.6">
@@ -18938,13 +18949,13 @@
       </c>
       <c r="H312"/>
       <c r="I312" s="1" t="s">
-        <v>1791</v>
+        <v>1786</v>
       </c>
       <c r="J312" s="26" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="K312" s="1" t="s">
-        <v>1729</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="313" spans="1:11">
@@ -18957,7 +18968,7 @@
         <v>687</v>
       </c>
       <c r="I313" s="9" t="s">
-        <v>1882</v>
+        <v>1873</v>
       </c>
       <c r="J313" s="1" t="s">
         <v>759</v>
@@ -19004,7 +19015,7 @@
         <v>687</v>
       </c>
       <c r="I316" s="9" t="s">
-        <v>1792</v>
+        <v>1787</v>
       </c>
       <c r="J316" s="26"/>
       <c r="K316" s="53" t="s">
@@ -19020,7 +19031,7 @@
         <v>741</v>
       </c>
       <c r="I317" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J317" s="26" t="s">
         <v>761</v>
@@ -19039,7 +19050,7 @@
         <v>687</v>
       </c>
       <c r="I318" s="9" t="s">
-        <v>1794</v>
+        <v>1789</v>
       </c>
       <c r="J318" s="26"/>
       <c r="K318" s="53" t="s">
@@ -19055,7 +19066,7 @@
         <v>741</v>
       </c>
       <c r="I319" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J319" s="26" t="s">
         <v>761</v>
@@ -19074,7 +19085,7 @@
         <v>687</v>
       </c>
       <c r="I320" s="9" t="s">
-        <v>1795</v>
+        <v>1790</v>
       </c>
       <c r="J320" s="26"/>
       <c r="K320" s="53" t="s">
@@ -19090,7 +19101,7 @@
         <v>741</v>
       </c>
       <c r="I321" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J321" s="26" t="s">
         <v>761</v>
@@ -19109,7 +19120,7 @@
         <v>687</v>
       </c>
       <c r="I322" s="9" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="J322" s="26"/>
       <c r="K322" s="53" t="s">
@@ -19125,7 +19136,7 @@
         <v>741</v>
       </c>
       <c r="I323" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J323" s="26" t="s">
         <v>761</v>
@@ -19144,7 +19155,7 @@
         <v>687</v>
       </c>
       <c r="I324" s="9" t="s">
-        <v>1797</v>
+        <v>1792</v>
       </c>
       <c r="J324" s="26"/>
       <c r="K324" s="53" t="s">
@@ -19160,7 +19171,7 @@
         <v>741</v>
       </c>
       <c r="I325" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J325" s="26" t="s">
         <v>761</v>
@@ -19179,7 +19190,7 @@
         <v>687</v>
       </c>
       <c r="I326" s="9" t="s">
-        <v>1798</v>
+        <v>1793</v>
       </c>
       <c r="J326" s="26"/>
       <c r="K326" s="53" t="s">
@@ -19195,7 +19206,7 @@
         <v>741</v>
       </c>
       <c r="I327" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J327" s="26" t="s">
         <v>761</v>
@@ -19214,7 +19225,7 @@
         <v>687</v>
       </c>
       <c r="I328" s="9" t="s">
-        <v>1799</v>
+        <v>1794</v>
       </c>
       <c r="J328" s="26"/>
       <c r="K328" s="53" t="s">
@@ -19230,7 +19241,7 @@
         <v>741</v>
       </c>
       <c r="I329" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J329" s="26" t="s">
         <v>761</v>
@@ -19249,7 +19260,7 @@
         <v>687</v>
       </c>
       <c r="I330" s="9" t="s">
-        <v>1799</v>
+        <v>1794</v>
       </c>
       <c r="J330" s="26"/>
       <c r="K330" s="53" t="s">
@@ -19265,7 +19276,7 @@
         <v>741</v>
       </c>
       <c r="I331" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J331" s="26" t="s">
         <v>761</v>
@@ -19283,7 +19294,7 @@
         <v>741</v>
       </c>
       <c r="I332" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J332" s="26" t="s">
         <v>761</v>
@@ -19301,7 +19312,7 @@
         <v>741</v>
       </c>
       <c r="I333" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J333" s="26" t="s">
         <v>761</v>
@@ -19320,7 +19331,7 @@
         <v>687</v>
       </c>
       <c r="I334" s="9" t="s">
-        <v>1800</v>
+        <v>1795</v>
       </c>
       <c r="J334" s="26"/>
       <c r="K334" s="53" t="s">
@@ -19336,7 +19347,7 @@
         <v>741</v>
       </c>
       <c r="I335" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J335" s="26" t="s">
         <v>761</v>
@@ -19355,7 +19366,7 @@
         <v>687</v>
       </c>
       <c r="I336" s="9" t="s">
-        <v>1801</v>
+        <v>1796</v>
       </c>
       <c r="J336" s="26"/>
       <c r="K336" s="53" t="s">
@@ -19371,7 +19382,7 @@
         <v>741</v>
       </c>
       <c r="I337" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J337" s="26" t="s">
         <v>761</v>
@@ -19390,7 +19401,7 @@
         <v>687</v>
       </c>
       <c r="I338" s="9" t="s">
-        <v>1802</v>
+        <v>1797</v>
       </c>
       <c r="J338" s="26"/>
       <c r="K338" s="53" t="s">
@@ -19406,7 +19417,7 @@
         <v>741</v>
       </c>
       <c r="I339" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J339" s="26" t="s">
         <v>761</v>
@@ -19425,7 +19436,7 @@
         <v>687</v>
       </c>
       <c r="I340" s="9" t="s">
-        <v>1803</v>
+        <v>1798</v>
       </c>
       <c r="J340" s="26"/>
       <c r="K340" s="53" t="s">
@@ -19441,7 +19452,7 @@
         <v>741</v>
       </c>
       <c r="I341" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J341" s="26" t="s">
         <v>761</v>
@@ -19460,7 +19471,7 @@
         <v>687</v>
       </c>
       <c r="I342" s="9" t="s">
-        <v>1804</v>
+        <v>1799</v>
       </c>
       <c r="J342" s="26"/>
       <c r="K342" s="53" t="s">
@@ -19476,7 +19487,7 @@
         <v>741</v>
       </c>
       <c r="I343" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J343" s="26" t="s">
         <v>761</v>
@@ -19495,7 +19506,7 @@
         <v>687</v>
       </c>
       <c r="I344" s="9" t="s">
-        <v>1798</v>
+        <v>1793</v>
       </c>
       <c r="J344" s="26"/>
       <c r="K344" s="53" t="s">
@@ -19511,7 +19522,7 @@
         <v>741</v>
       </c>
       <c r="I345" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J345" s="26" t="s">
         <v>761</v>
@@ -19530,7 +19541,7 @@
         <v>687</v>
       </c>
       <c r="I346" s="9" t="s">
-        <v>1805</v>
+        <v>1800</v>
       </c>
       <c r="J346" s="26"/>
       <c r="K346" s="53" t="s">
@@ -19546,7 +19557,7 @@
         <v>741</v>
       </c>
       <c r="I347" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J347" s="26" t="s">
         <v>761</v>
@@ -19565,7 +19576,7 @@
         <v>687</v>
       </c>
       <c r="I348" s="9" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="J348" s="26"/>
       <c r="K348" s="53" t="s">
@@ -19581,7 +19592,7 @@
         <v>741</v>
       </c>
       <c r="I349" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J349" s="26" t="s">
         <v>761</v>
@@ -19600,7 +19611,7 @@
         <v>687</v>
       </c>
       <c r="I350" s="9" t="s">
-        <v>1806</v>
+        <v>1801</v>
       </c>
       <c r="J350" s="26"/>
       <c r="K350" s="53" t="s">
@@ -19616,7 +19627,7 @@
         <v>741</v>
       </c>
       <c r="I351" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J351" s="26" t="s">
         <v>761</v>
@@ -19635,7 +19646,7 @@
         <v>687</v>
       </c>
       <c r="I352" s="9" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="J352" s="26"/>
       <c r="K352" s="53" t="s">
@@ -19651,7 +19662,7 @@
         <v>741</v>
       </c>
       <c r="I353" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J353" s="26" t="s">
         <v>761</v>
@@ -19670,7 +19681,7 @@
         <v>687</v>
       </c>
       <c r="I354" s="9" t="s">
-        <v>1806</v>
+        <v>1801</v>
       </c>
       <c r="J354" s="26"/>
       <c r="K354" s="53" t="s">
@@ -19686,7 +19697,7 @@
         <v>741</v>
       </c>
       <c r="I355" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J355" s="26" t="s">
         <v>761</v>
@@ -19705,7 +19716,7 @@
         <v>687</v>
       </c>
       <c r="I356" s="9" t="s">
-        <v>1800</v>
+        <v>1795</v>
       </c>
       <c r="J356" s="26"/>
       <c r="K356" s="53" t="s">
@@ -19721,7 +19732,7 @@
         <v>741</v>
       </c>
       <c r="I357" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J357" s="26" t="s">
         <v>761</v>
@@ -19740,7 +19751,7 @@
         <v>687</v>
       </c>
       <c r="I358" s="9" t="s">
-        <v>1798</v>
+        <v>1793</v>
       </c>
       <c r="J358" s="26"/>
       <c r="K358" s="53" t="s">
@@ -19756,7 +19767,7 @@
         <v>741</v>
       </c>
       <c r="I359" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J359" s="26" t="s">
         <v>761</v>
@@ -19775,7 +19786,7 @@
         <v>687</v>
       </c>
       <c r="I360" s="9" t="s">
-        <v>1792</v>
+        <v>1787</v>
       </c>
       <c r="J360" s="26"/>
       <c r="K360" s="53" t="s">
@@ -19791,7 +19802,7 @@
         <v>741</v>
       </c>
       <c r="I361" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J361" s="26" t="s">
         <v>761</v>
@@ -19810,7 +19821,7 @@
         <v>687</v>
       </c>
       <c r="I362" s="9" t="s">
-        <v>1792</v>
+        <v>1787</v>
       </c>
       <c r="J362" s="26"/>
       <c r="K362" s="53" t="s">
@@ -19826,7 +19837,7 @@
         <v>741</v>
       </c>
       <c r="I363" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J363" s="26" t="s">
         <v>761</v>
@@ -19845,7 +19856,7 @@
         <v>687</v>
       </c>
       <c r="I364" s="9" t="s">
-        <v>1806</v>
+        <v>1801</v>
       </c>
       <c r="J364" s="26"/>
       <c r="K364" s="53" t="s">
@@ -19861,7 +19872,7 @@
         <v>741</v>
       </c>
       <c r="I365" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J365" s="26" t="s">
         <v>761</v>
@@ -19880,7 +19891,7 @@
         <v>687</v>
       </c>
       <c r="I366" s="9" t="s">
-        <v>1807</v>
+        <v>1802</v>
       </c>
       <c r="J366" s="26"/>
       <c r="K366" s="53" t="s">
@@ -19896,7 +19907,7 @@
         <v>741</v>
       </c>
       <c r="I367" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J367" s="26" t="s">
         <v>761</v>
@@ -19915,7 +19926,7 @@
         <v>687</v>
       </c>
       <c r="I368" s="9" t="s">
-        <v>1801</v>
+        <v>1796</v>
       </c>
       <c r="J368" s="26"/>
       <c r="K368" s="53" t="s">
@@ -19931,7 +19942,7 @@
         <v>741</v>
       </c>
       <c r="I369" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J369" s="26" t="s">
         <v>761</v>
@@ -19950,7 +19961,7 @@
         <v>687</v>
       </c>
       <c r="I370" s="9" t="s">
-        <v>1799</v>
+        <v>1794</v>
       </c>
       <c r="J370" s="26"/>
       <c r="K370" s="53" t="s">
@@ -19966,7 +19977,7 @@
         <v>741</v>
       </c>
       <c r="I371" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J371" s="26" t="s">
         <v>761</v>
@@ -19985,7 +19996,7 @@
         <v>687</v>
       </c>
       <c r="I372" s="9" t="s">
-        <v>1799</v>
+        <v>1794</v>
       </c>
       <c r="J372" s="26"/>
       <c r="K372" s="53" t="s">
@@ -20001,7 +20012,7 @@
         <v>741</v>
       </c>
       <c r="I373" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J373" s="26" t="s">
         <v>761</v>
@@ -20019,7 +20030,7 @@
         <v>687</v>
       </c>
       <c r="I374" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J374" s="26" t="s">
         <v>761</v>
@@ -20038,7 +20049,7 @@
         <v>687</v>
       </c>
       <c r="I375" s="9" t="s">
-        <v>1808</v>
+        <v>1803</v>
       </c>
       <c r="J375" s="26"/>
       <c r="K375" s="53" t="s">
@@ -20054,7 +20065,7 @@
         <v>741</v>
       </c>
       <c r="I376" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J376" s="26" t="s">
         <v>761</v>
@@ -20073,7 +20084,7 @@
         <v>687</v>
       </c>
       <c r="I377" s="9" t="s">
-        <v>1809</v>
+        <v>1804</v>
       </c>
       <c r="J377" s="26"/>
       <c r="K377" s="53" t="s">
@@ -20089,7 +20100,7 @@
         <v>741</v>
       </c>
       <c r="I378" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J378" s="26" t="s">
         <v>761</v>
@@ -20108,7 +20119,7 @@
         <v>687</v>
       </c>
       <c r="I379" s="9" t="s">
-        <v>1808</v>
+        <v>1803</v>
       </c>
       <c r="J379" s="26"/>
       <c r="K379" s="53" t="s">
@@ -20124,7 +20135,7 @@
         <v>741</v>
       </c>
       <c r="I380" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J380" s="26" t="s">
         <v>761</v>
@@ -20143,7 +20154,7 @@
         <v>687</v>
       </c>
       <c r="I381" s="9" t="s">
-        <v>1810</v>
+        <v>1805</v>
       </c>
       <c r="J381" s="26"/>
       <c r="K381" s="53" t="s">
@@ -20159,7 +20170,7 @@
         <v>741</v>
       </c>
       <c r="I382" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J382" s="26" t="s">
         <v>761</v>
@@ -20178,7 +20189,7 @@
         <v>687</v>
       </c>
       <c r="I383" s="9" t="s">
-        <v>1810</v>
+        <v>1805</v>
       </c>
       <c r="J383" s="26"/>
       <c r="K383" s="53" t="s">
@@ -20194,7 +20205,7 @@
         <v>741</v>
       </c>
       <c r="I384" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J384" s="26" t="s">
         <v>761</v>
@@ -20213,7 +20224,7 @@
         <v>687</v>
       </c>
       <c r="I385" s="9" t="s">
-        <v>1811</v>
+        <v>1806</v>
       </c>
       <c r="J385" s="26"/>
       <c r="K385" s="53" t="s">
@@ -20229,7 +20240,7 @@
         <v>741</v>
       </c>
       <c r="I386" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J386" s="26" t="s">
         <v>761</v>
@@ -20248,7 +20259,7 @@
         <v>687</v>
       </c>
       <c r="I387" s="9" t="s">
-        <v>1812</v>
+        <v>1807</v>
       </c>
       <c r="J387" s="26"/>
       <c r="K387" s="53" t="s">
@@ -20264,7 +20275,7 @@
         <v>741</v>
       </c>
       <c r="I388" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J388" s="26" t="s">
         <v>761</v>
@@ -20282,7 +20293,7 @@
         <v>687</v>
       </c>
       <c r="I389" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J389" s="26" t="s">
         <v>761</v>
@@ -20301,7 +20312,7 @@
         <v>687</v>
       </c>
       <c r="I390" s="9" t="s">
-        <v>1813</v>
+        <v>1808</v>
       </c>
       <c r="J390" s="26"/>
       <c r="K390" s="53" t="s">
@@ -20317,7 +20328,7 @@
         <v>741</v>
       </c>
       <c r="I391" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J391" s="26" t="s">
         <v>761</v>
@@ -20336,7 +20347,7 @@
         <v>687</v>
       </c>
       <c r="I392" s="9" t="s">
-        <v>1814</v>
+        <v>1809</v>
       </c>
       <c r="J392" s="26"/>
       <c r="K392" s="53" t="s">
@@ -20352,7 +20363,7 @@
         <v>741</v>
       </c>
       <c r="I393" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J393" s="26" t="s">
         <v>761</v>
@@ -20371,7 +20382,7 @@
         <v>687</v>
       </c>
       <c r="I394" s="9" t="s">
-        <v>1815</v>
+        <v>1810</v>
       </c>
       <c r="J394" s="26"/>
       <c r="K394" s="53" t="s">
@@ -20387,7 +20398,7 @@
         <v>741</v>
       </c>
       <c r="I395" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J395" s="26" t="s">
         <v>761</v>
@@ -20405,7 +20416,7 @@
         <v>687</v>
       </c>
       <c r="I396" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J396" s="26" t="s">
         <v>761</v>
@@ -20424,7 +20435,7 @@
         <v>687</v>
       </c>
       <c r="I397" s="9" t="s">
-        <v>1816</v>
+        <v>1811</v>
       </c>
       <c r="J397" s="26"/>
       <c r="K397" s="53" t="s">
@@ -20440,7 +20451,7 @@
         <v>741</v>
       </c>
       <c r="I398" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J398" s="26" t="s">
         <v>761</v>
@@ -20459,7 +20470,7 @@
         <v>687</v>
       </c>
       <c r="I399" s="9" t="s">
-        <v>1808</v>
+        <v>1803</v>
       </c>
       <c r="J399" s="26"/>
       <c r="K399" s="53" t="s">
@@ -20475,7 +20486,7 @@
         <v>741</v>
       </c>
       <c r="I400" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J400" s="26" t="s">
         <v>761</v>
@@ -20494,7 +20505,7 @@
         <v>687</v>
       </c>
       <c r="I401" s="9" t="s">
-        <v>1794</v>
+        <v>1789</v>
       </c>
       <c r="J401" s="26"/>
       <c r="K401" s="53" t="s">
@@ -20510,7 +20521,7 @@
         <v>741</v>
       </c>
       <c r="I402" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J402" s="26" t="s">
         <v>761</v>
@@ -20529,7 +20540,7 @@
         <v>687</v>
       </c>
       <c r="I403" s="9" t="s">
-        <v>1794</v>
+        <v>1789</v>
       </c>
       <c r="J403" s="26"/>
       <c r="K403" s="53" t="s">
@@ -20545,7 +20556,7 @@
         <v>741</v>
       </c>
       <c r="I404" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J404" s="26" t="s">
         <v>761</v>
@@ -20564,7 +20575,7 @@
         <v>687</v>
       </c>
       <c r="I405" s="9" t="s">
-        <v>1817</v>
+        <v>1812</v>
       </c>
       <c r="J405" s="26"/>
       <c r="K405" s="53" t="s">
@@ -20580,7 +20591,7 @@
         <v>741</v>
       </c>
       <c r="I406" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J406" s="26" t="s">
         <v>761</v>
@@ -20599,7 +20610,7 @@
         <v>687</v>
       </c>
       <c r="I407" s="9" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="J407" s="26"/>
       <c r="K407" s="53" t="s">
@@ -20615,7 +20626,7 @@
         <v>741</v>
       </c>
       <c r="I408" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J408" s="26" t="s">
         <v>761</v>
@@ -20634,7 +20645,7 @@
         <v>687</v>
       </c>
       <c r="I409" s="9" t="s">
-        <v>1818</v>
+        <v>1813</v>
       </c>
       <c r="J409" s="26"/>
       <c r="K409" s="53" t="s">
@@ -20650,7 +20661,7 @@
         <v>741</v>
       </c>
       <c r="I410" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J410" s="26" t="s">
         <v>761</v>
@@ -20669,7 +20680,7 @@
         <v>687</v>
       </c>
       <c r="I411" s="9" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="J411" s="26"/>
       <c r="K411" s="53" t="s">
@@ -20685,7 +20696,7 @@
         <v>741</v>
       </c>
       <c r="I412" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J412" s="26" t="s">
         <v>761</v>
@@ -20704,7 +20715,7 @@
         <v>687</v>
       </c>
       <c r="I413" s="9" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="J413" s="26"/>
       <c r="K413" s="53" t="s">
@@ -20720,7 +20731,7 @@
         <v>741</v>
       </c>
       <c r="I414" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J414" s="26" t="s">
         <v>761</v>
@@ -20739,7 +20750,7 @@
         <v>687</v>
       </c>
       <c r="I415" s="9" t="s">
-        <v>1819</v>
+        <v>1814</v>
       </c>
       <c r="J415" s="26"/>
       <c r="K415" s="53" t="s">
@@ -20755,7 +20766,7 @@
         <v>741</v>
       </c>
       <c r="I416" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J416" s="26" t="s">
         <v>761</v>
@@ -20774,7 +20785,7 @@
         <v>687</v>
       </c>
       <c r="I417" s="9" t="s">
-        <v>1799</v>
+        <v>1794</v>
       </c>
       <c r="J417" s="26"/>
       <c r="K417" s="53" t="s">
@@ -20790,7 +20801,7 @@
         <v>741</v>
       </c>
       <c r="I418" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J418" s="26" t="s">
         <v>761</v>
@@ -20809,7 +20820,7 @@
         <v>687</v>
       </c>
       <c r="I419" s="9" t="s">
-        <v>1799</v>
+        <v>1794</v>
       </c>
       <c r="J419" s="26"/>
       <c r="K419" s="53" t="s">
@@ -20825,7 +20836,7 @@
         <v>741</v>
       </c>
       <c r="I420" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J420" s="26" t="s">
         <v>761</v>
@@ -20844,7 +20855,7 @@
         <v>687</v>
       </c>
       <c r="I421" s="9" t="s">
-        <v>1799</v>
+        <v>1794</v>
       </c>
       <c r="J421" s="26"/>
       <c r="K421" s="53" t="s">
@@ -20860,7 +20871,7 @@
         <v>741</v>
       </c>
       <c r="I422" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J422" s="26" t="s">
         <v>761</v>
@@ -20879,7 +20890,7 @@
         <v>687</v>
       </c>
       <c r="I423" s="9" t="s">
-        <v>1817</v>
+        <v>1812</v>
       </c>
       <c r="J423" s="26"/>
       <c r="K423" s="53" t="s">
@@ -20895,7 +20906,7 @@
         <v>741</v>
       </c>
       <c r="I424" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J424" s="26" t="s">
         <v>761</v>
@@ -20914,7 +20925,7 @@
         <v>687</v>
       </c>
       <c r="I425" s="9" t="s">
-        <v>1817</v>
+        <v>1812</v>
       </c>
       <c r="J425" s="26"/>
       <c r="K425" s="53" t="s">
@@ -20930,7 +20941,7 @@
         <v>741</v>
       </c>
       <c r="I426" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J426" s="26" t="s">
         <v>761</v>
@@ -20949,7 +20960,7 @@
         <v>687</v>
       </c>
       <c r="I427" s="9" t="s">
-        <v>1820</v>
+        <v>1815</v>
       </c>
       <c r="J427" s="26"/>
       <c r="K427" s="53" t="s">
@@ -20965,7 +20976,7 @@
         <v>741</v>
       </c>
       <c r="I428" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J428" s="26" t="s">
         <v>761</v>
@@ -20984,7 +20995,7 @@
         <v>687</v>
       </c>
       <c r="I429" s="9" t="s">
-        <v>1800</v>
+        <v>1795</v>
       </c>
       <c r="J429" s="26"/>
       <c r="K429" s="53" t="s">
@@ -21000,7 +21011,7 @@
         <v>741</v>
       </c>
       <c r="I430" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J430" s="26" t="s">
         <v>761</v>
@@ -21019,7 +21030,7 @@
         <v>687</v>
       </c>
       <c r="I431" s="9" t="s">
-        <v>1817</v>
+        <v>1812</v>
       </c>
       <c r="J431" s="26"/>
       <c r="K431" s="53" t="s">
@@ -21035,7 +21046,7 @@
         <v>741</v>
       </c>
       <c r="I432" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J432" s="26" t="s">
         <v>761</v>
@@ -21053,7 +21064,7 @@
         <v>741</v>
       </c>
       <c r="I433" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J433" s="26" t="s">
         <v>761</v>
@@ -21071,7 +21082,7 @@
         <v>741</v>
       </c>
       <c r="I434" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J434" s="26" t="s">
         <v>761</v>
@@ -21090,7 +21101,7 @@
         <v>741</v>
       </c>
       <c r="I435" s="9" t="s">
-        <v>1817</v>
+        <v>1812</v>
       </c>
       <c r="J435" s="26"/>
       <c r="K435" s="53" t="s">
@@ -21106,7 +21117,7 @@
         <v>741</v>
       </c>
       <c r="I436" s="9" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="J436" s="26" t="s">
         <v>761</v>
@@ -21115,7 +21126,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="437" spans="1:11">
+    <row r="437" spans="1:11" ht="43.2">
       <c r="A437" s="11" t="s">
         <v>377</v>
       </c>
@@ -21124,16 +21135,16 @@
         <v>687</v>
       </c>
       <c r="I437" s="9" t="s">
-        <v>1821</v>
+        <v>1906</v>
       </c>
       <c r="J437" s="26" t="s">
-        <v>1709</v>
+        <v>1912</v>
       </c>
       <c r="K437" t="s">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="438" spans="1:11">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="438" spans="1:11" ht="43.2">
       <c r="A438" s="11" t="s">
         <v>429</v>
       </c>
@@ -21142,16 +21153,16 @@
         <v>687</v>
       </c>
       <c r="I438" s="9" t="s">
-        <v>1822</v>
+        <v>1907</v>
       </c>
       <c r="J438" s="26" t="s">
-        <v>1709</v>
+        <v>1912</v>
       </c>
       <c r="K438" t="s">
-        <v>1701</v>
-      </c>
-    </row>
-    <row r="439" spans="1:11">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="439" spans="1:11" ht="43.2">
       <c r="A439" s="11" t="s">
         <v>381</v>
       </c>
@@ -21160,16 +21171,16 @@
         <v>687</v>
       </c>
       <c r="I439" s="9" t="s">
-        <v>1823</v>
+        <v>1908</v>
       </c>
       <c r="J439" s="26" t="s">
-        <v>1709</v>
+        <v>1912</v>
       </c>
       <c r="K439" t="s">
-        <v>1702</v>
-      </c>
-    </row>
-    <row r="440" spans="1:11">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="440" spans="1:11" ht="57.6">
       <c r="A440" s="11" t="s">
         <v>379</v>
       </c>
@@ -21178,16 +21189,16 @@
         <v>687</v>
       </c>
       <c r="I440" s="9" t="s">
-        <v>1822</v>
+        <v>1909</v>
       </c>
       <c r="J440" s="26" t="s">
-        <v>1709</v>
+        <v>1911</v>
       </c>
       <c r="K440" t="s">
-        <v>1703</v>
-      </c>
-    </row>
-    <row r="441" spans="1:11">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="441" spans="1:11" ht="43.2">
       <c r="A441" s="11" t="s">
         <v>430</v>
       </c>
@@ -21196,16 +21207,16 @@
         <v>687</v>
       </c>
       <c r="I441" s="9" t="s">
-        <v>1822</v>
+        <v>1907</v>
       </c>
       <c r="J441" s="26" t="s">
-        <v>1709</v>
+        <v>1912</v>
       </c>
       <c r="K441" t="s">
-        <v>1704</v>
-      </c>
-    </row>
-    <row r="442" spans="1:11">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="442" spans="1:11" ht="57.6">
       <c r="A442" s="11" t="s">
         <v>378</v>
       </c>
@@ -21214,16 +21225,16 @@
         <v>687</v>
       </c>
       <c r="I442" s="9" t="s">
-        <v>1822</v>
+        <v>1909</v>
       </c>
       <c r="J442" s="26" t="s">
-        <v>1709</v>
+        <v>1911</v>
       </c>
       <c r="K442" t="s">
-        <v>1705</v>
-      </c>
-    </row>
-    <row r="443" spans="1:11">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="443" spans="1:11" ht="43.2">
       <c r="A443" s="11" t="s">
         <v>399</v>
       </c>
@@ -21232,16 +21243,16 @@
         <v>687</v>
       </c>
       <c r="I443" s="9" t="s">
-        <v>1822</v>
+        <v>1907</v>
       </c>
       <c r="J443" s="26" t="s">
-        <v>1709</v>
+        <v>1912</v>
       </c>
       <c r="K443" t="s">
-        <v>1706</v>
-      </c>
-    </row>
-    <row r="444" spans="1:11">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="444" spans="1:11" ht="43.2">
       <c r="A444" s="11" t="s">
         <v>403</v>
       </c>
@@ -21250,16 +21261,16 @@
         <v>687</v>
       </c>
       <c r="I444" s="9" t="s">
-        <v>1824</v>
+        <v>1910</v>
       </c>
       <c r="J444" s="26" t="s">
-        <v>1709</v>
+        <v>1912</v>
       </c>
       <c r="K444" t="s">
-        <v>1707</v>
-      </c>
-    </row>
-    <row r="445" spans="1:11">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="445" spans="1:11" ht="43.2">
       <c r="A445" s="11" t="s">
         <v>589</v>
       </c>
@@ -21268,13 +21279,13 @@
         <v>687</v>
       </c>
       <c r="I445" s="9" t="s">
-        <v>1822</v>
+        <v>1907</v>
       </c>
       <c r="J445" s="26" t="s">
-        <v>1709</v>
+        <v>1912</v>
       </c>
       <c r="K445" t="s">
-        <v>1708</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="446" spans="1:11">
@@ -22528,7 +22539,7 @@
         <v>443</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1825</v>
+        <v>1816</v>
       </c>
       <c r="D9" t="s">
         <v>1390</v>
@@ -22542,7 +22553,7 @@
         <v>737</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1826</v>
+        <v>1817</v>
       </c>
       <c r="D10" t="s">
         <v>1391</v>
@@ -22556,7 +22567,7 @@
         <v>737</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1826</v>
+        <v>1817</v>
       </c>
       <c r="D11" t="s">
         <v>1392</v>
@@ -22570,7 +22581,7 @@
         <v>737</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>1826</v>
+        <v>1817</v>
       </c>
       <c r="D12" t="s">
         <v>1393</v>
@@ -22584,7 +22595,7 @@
         <v>261</v>
       </c>
       <c r="C13" t="s">
-        <v>1893</v>
+        <v>1884</v>
       </c>
       <c r="D13" t="s">
         <v>1394</v>
@@ -22598,7 +22609,7 @@
         <v>245</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1827</v>
+        <v>1818</v>
       </c>
       <c r="D14" t="s">
         <v>1395</v>
@@ -22612,7 +22623,7 @@
         <v>272</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>1828</v>
+        <v>1819</v>
       </c>
       <c r="D15" t="s">
         <v>1396</v>
@@ -22626,7 +22637,7 @@
         <v>261</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>1893</v>
+        <v>1884</v>
       </c>
       <c r="D16" t="s">
         <v>1397</v>
@@ -22640,7 +22651,7 @@
         <v>273</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>1894</v>
+        <v>1885</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>1398</v>
@@ -22654,7 +22665,7 @@
         <v>229</v>
       </c>
       <c r="C18" t="s">
-        <v>1895</v>
+        <v>1886</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>1399</v>
@@ -22668,7 +22679,7 @@
         <v>242</v>
       </c>
       <c r="C19" t="s">
-        <v>1829</v>
+        <v>1820</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>1400</v>
@@ -22682,7 +22693,7 @@
         <v>227</v>
       </c>
       <c r="C20" t="s">
-        <v>1830</v>
+        <v>1821</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>1401</v>
@@ -22696,7 +22707,7 @@
         <v>274</v>
       </c>
       <c r="C21" t="s">
-        <v>1831</v>
+        <v>1822</v>
       </c>
       <c r="D21" t="s">
         <v>1402</v>
@@ -22710,7 +22721,7 @@
         <v>275</v>
       </c>
       <c r="C22" t="s">
-        <v>1832</v>
+        <v>1823</v>
       </c>
       <c r="D22" t="s">
         <v>1403</v>
@@ -22724,7 +22735,7 @@
         <v>228</v>
       </c>
       <c r="C23" t="s">
-        <v>1896</v>
+        <v>1887</v>
       </c>
       <c r="D23" t="s">
         <v>1404</v>
@@ -22738,7 +22749,7 @@
         <v>250</v>
       </c>
       <c r="C24" t="s">
-        <v>1833</v>
+        <v>1824</v>
       </c>
       <c r="D24" t="s">
         <v>1405</v>
@@ -22752,7 +22763,7 @@
         <v>249</v>
       </c>
       <c r="C25" t="s">
-        <v>1834</v>
+        <v>1825</v>
       </c>
       <c r="D25" t="s">
         <v>1406</v>
@@ -22766,7 +22777,7 @@
         <v>244</v>
       </c>
       <c r="C26" t="s">
-        <v>1835</v>
+        <v>1826</v>
       </c>
       <c r="D26" t="s">
         <v>1407</v>
@@ -22780,7 +22791,7 @@
         <v>244</v>
       </c>
       <c r="C27" t="s">
-        <v>1835</v>
+        <v>1826</v>
       </c>
       <c r="D27" t="s">
         <v>1408</v>
@@ -22794,7 +22805,7 @@
         <v>262</v>
       </c>
       <c r="C28" t="s">
-        <v>1836</v>
+        <v>1827</v>
       </c>
       <c r="D28" t="s">
         <v>1409</v>
@@ -22808,7 +22819,7 @@
         <v>250</v>
       </c>
       <c r="C29" t="s">
-        <v>1833</v>
+        <v>1824</v>
       </c>
       <c r="D29" t="s">
         <v>1410</v>
@@ -22822,7 +22833,7 @@
         <v>263</v>
       </c>
       <c r="C30" t="s">
-        <v>1897</v>
+        <v>1888</v>
       </c>
       <c r="D30" t="s">
         <v>1411</v>
@@ -22836,7 +22847,7 @@
         <v>307</v>
       </c>
       <c r="C31" t="s">
-        <v>1837</v>
+        <v>1828</v>
       </c>
       <c r="D31" t="s">
         <v>1412</v>
@@ -22850,7 +22861,7 @@
         <v>245</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>1827</v>
+        <v>1818</v>
       </c>
       <c r="D32" t="s">
         <v>1413</v>
@@ -22864,7 +22875,7 @@
         <v>264</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>1898</v>
+        <v>1889</v>
       </c>
       <c r="D33" t="s">
         <v>1414</v>
@@ -22878,7 +22889,7 @@
         <v>265</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>1899</v>
+        <v>1890</v>
       </c>
       <c r="D34" s="53" t="s">
         <v>1415</v>
@@ -22892,7 +22903,7 @@
         <v>736</v>
       </c>
       <c r="C35" s="41" t="s">
-        <v>1838</v>
+        <v>1829</v>
       </c>
       <c r="D35" t="s">
         <v>1416</v>
@@ -22907,7 +22918,7 @@
         <v>266</v>
       </c>
       <c r="C36" t="s">
-        <v>1834</v>
+        <v>1825</v>
       </c>
       <c r="D36" s="53" t="s">
         <v>1417</v>
@@ -22921,7 +22932,7 @@
         <v>736</v>
       </c>
       <c r="C37" s="41" t="s">
-        <v>1838</v>
+        <v>1829</v>
       </c>
       <c r="D37" t="s">
         <v>1418</v>
@@ -22936,7 +22947,7 @@
         <v>244</v>
       </c>
       <c r="C38" t="s">
-        <v>1835</v>
+        <v>1826</v>
       </c>
       <c r="D38" t="s">
         <v>1419</v>
@@ -22950,7 +22961,7 @@
         <v>267</v>
       </c>
       <c r="C39" t="s">
-        <v>1839</v>
+        <v>1830</v>
       </c>
       <c r="D39" t="s">
         <v>1420</v>
@@ -22964,7 +22975,7 @@
         <v>268</v>
       </c>
       <c r="C40" t="s">
-        <v>1900</v>
+        <v>1891</v>
       </c>
       <c r="D40" t="s">
         <v>1421</v>
@@ -22978,7 +22989,7 @@
         <v>241</v>
       </c>
       <c r="C41" t="s">
-        <v>1840</v>
+        <v>1831</v>
       </c>
       <c r="D41" t="s">
         <v>1422</v>
@@ -22992,7 +23003,7 @@
         <v>231</v>
       </c>
       <c r="C42" t="s">
-        <v>1841</v>
+        <v>1832</v>
       </c>
       <c r="D42" t="s">
         <v>1423</v>
@@ -23006,7 +23017,7 @@
         <v>723</v>
       </c>
       <c r="C43" t="s">
-        <v>1842</v>
+        <v>1833</v>
       </c>
       <c r="D43" t="s">
         <v>1424</v>
@@ -23020,7 +23031,7 @@
         <v>723</v>
       </c>
       <c r="C44" t="s">
-        <v>1842</v>
+        <v>1833</v>
       </c>
       <c r="D44" t="s">
         <v>1425</v>
@@ -23034,7 +23045,7 @@
         <v>269</v>
       </c>
       <c r="C45" t="s">
-        <v>1843</v>
+        <v>1834</v>
       </c>
       <c r="D45" t="s">
         <v>1426</v>
@@ -23048,7 +23059,7 @@
         <v>241</v>
       </c>
       <c r="C46" t="s">
-        <v>1840</v>
+        <v>1831</v>
       </c>
       <c r="D46" t="s">
         <v>1427</v>
@@ -23062,7 +23073,7 @@
         <v>249</v>
       </c>
       <c r="C47" t="s">
-        <v>1834</v>
+        <v>1825</v>
       </c>
       <c r="D47" t="s">
         <v>1428</v>
@@ -23076,7 +23087,7 @@
         <v>717</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>1844</v>
+        <v>1835</v>
       </c>
       <c r="D48" t="s">
         <v>1429</v>
@@ -23090,7 +23101,7 @@
         <v>270</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>1845</v>
+        <v>1836</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>1430</v>
@@ -23104,7 +23115,7 @@
         <v>1523</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>1846</v>
+        <v>1837</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>1524</v>
@@ -23118,7 +23129,7 @@
         <v>718</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>1847</v>
+        <v>1838</v>
       </c>
       <c r="D51" t="s">
         <v>1431</v>
@@ -23132,7 +23143,7 @@
         <v>240</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>1848</v>
+        <v>1839</v>
       </c>
       <c r="D52" t="s">
         <v>1432</v>
@@ -23146,7 +23157,7 @@
         <v>719</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>1849</v>
+        <v>1840</v>
       </c>
       <c r="D53" t="s">
         <v>1433</v>
@@ -23160,7 +23171,7 @@
         <v>240</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>1848</v>
+        <v>1839</v>
       </c>
       <c r="D54" t="s">
         <v>1434</v>
@@ -23174,7 +23185,7 @@
         <v>242</v>
       </c>
       <c r="C55" t="s">
-        <v>1829</v>
+        <v>1820</v>
       </c>
       <c r="D55" t="s">
         <v>1435</v>
@@ -23188,7 +23199,7 @@
         <v>241</v>
       </c>
       <c r="C56" t="s">
-        <v>1840</v>
+        <v>1831</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>1436</v>
@@ -23202,7 +23213,7 @@
         <v>720</v>
       </c>
       <c r="C57" t="s">
-        <v>1901</v>
+        <v>1892</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>1437</v>
@@ -23216,7 +23227,7 @@
         <v>723</v>
       </c>
       <c r="C58" t="s">
-        <v>1842</v>
+        <v>1833</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>1438</v>
@@ -23230,7 +23241,7 @@
         <v>722</v>
       </c>
       <c r="C59" t="s">
-        <v>1902</v>
+        <v>1893</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>1439</v>
@@ -23244,7 +23255,7 @@
         <v>722</v>
       </c>
       <c r="C60" t="s">
-        <v>1902</v>
+        <v>1893</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>1440</v>
@@ -23258,7 +23269,7 @@
         <v>726</v>
       </c>
       <c r="C61" t="s">
-        <v>1903</v>
+        <v>1894</v>
       </c>
       <c r="D61" t="s">
         <v>1441</v>
@@ -23272,7 +23283,7 @@
         <v>728</v>
       </c>
       <c r="C62" t="s">
-        <v>1850</v>
+        <v>1841</v>
       </c>
       <c r="D62" t="s">
         <v>1442</v>
@@ -23286,7 +23297,7 @@
         <v>729</v>
       </c>
       <c r="C63" t="s">
-        <v>1851</v>
+        <v>1842</v>
       </c>
       <c r="D63" t="s">
         <v>1443</v>
@@ -23300,7 +23311,7 @@
         <v>732</v>
       </c>
       <c r="C64" t="s">
-        <v>1852</v>
+        <v>1843</v>
       </c>
       <c r="D64" t="s">
         <v>1444</v>
@@ -23314,7 +23325,7 @@
         <v>735</v>
       </c>
       <c r="C65" t="s">
-        <v>1853</v>
+        <v>1844</v>
       </c>
       <c r="D65" t="s">
         <v>1445</v>
@@ -23328,7 +23339,7 @@
         <v>241</v>
       </c>
       <c r="C66" t="s">
-        <v>1840</v>
+        <v>1831</v>
       </c>
       <c r="D66" t="s">
         <v>1446</v>
@@ -23342,7 +23353,7 @@
         <v>262</v>
       </c>
       <c r="C67" t="s">
-        <v>1836</v>
+        <v>1827</v>
       </c>
       <c r="D67" t="s">
         <v>1447</v>
@@ -23356,7 +23367,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>1836</v>
+        <v>1827</v>
       </c>
       <c r="D68" t="s">
         <v>1448</v>
@@ -23370,7 +23381,7 @@
         <v>442</v>
       </c>
       <c r="C69" t="s">
-        <v>1854</v>
+        <v>1845</v>
       </c>
       <c r="D69" t="s">
         <v>1449</v>
@@ -23384,7 +23395,7 @@
         <v>442</v>
       </c>
       <c r="C70" t="s">
-        <v>1854</v>
+        <v>1845</v>
       </c>
       <c r="D70" t="s">
         <v>1450</v>
@@ -23501,18 +23512,18 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="11" spans="1:4" s="60" customFormat="1">
-      <c r="A11" s="59" t="s">
+    <row r="11" spans="1:4" s="59" customFormat="1">
+      <c r="A11" s="58" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="60" t="s">
-        <v>1907</v>
-      </c>
-      <c r="C11" s="60" t="s">
-        <v>1908</v>
-      </c>
-      <c r="D11" s="60" t="s">
-        <v>1909</v>
+      <c r="B11" s="59" t="s">
+        <v>1898</v>
+      </c>
+      <c r="C11" s="59" t="s">
+        <v>1899</v>
+      </c>
+      <c r="D11" s="59" t="s">
+        <v>1900</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -23694,7 +23705,7 @@
         <v>251</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1883</v>
+        <v>1874</v>
       </c>
       <c r="D9" t="s">
         <v>1456</v>
@@ -23708,7 +23719,7 @@
         <v>304</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1884</v>
+        <v>1875</v>
       </c>
       <c r="D10" t="s">
         <v>1457</v>
@@ -23722,7 +23733,7 @@
         <v>305</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1885</v>
+        <v>1876</v>
       </c>
       <c r="D11" t="s">
         <v>1458</v>
@@ -23736,7 +23747,7 @@
         <v>765</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>1886</v>
+        <v>1877</v>
       </c>
       <c r="D12" t="s">
         <v>1459</v>
@@ -23750,7 +23761,7 @@
         <v>308</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1887</v>
+        <v>1878</v>
       </c>
       <c r="D13" t="s">
         <v>1460</v>
@@ -23764,7 +23775,7 @@
         <v>312</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1888</v>
+        <v>1879</v>
       </c>
       <c r="D14" t="s">
         <v>1461</v>
@@ -23778,7 +23789,7 @@
         <v>313</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>1889</v>
+        <v>1880</v>
       </c>
       <c r="D15" t="s">
         <v>1462</v>
@@ -23792,7 +23803,7 @@
         <v>354</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>1890</v>
+        <v>1881</v>
       </c>
       <c r="D16" t="s">
         <v>1463</v>
@@ -23806,7 +23817,7 @@
         <v>310</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>1891</v>
+        <v>1882</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>1464</v>
@@ -23820,7 +23831,7 @@
         <v>311</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>1892</v>
+        <v>1883</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>1465</v>
@@ -24129,13 +24140,13 @@
         <v>130</v>
       </c>
       <c r="B19" t="s">
-        <v>1904</v>
+        <v>1895</v>
       </c>
       <c r="C19" t="s">
-        <v>1905</v>
+        <v>1896</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1906</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -24236,16 +24247,16 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="6" t="s">
-        <v>1735</v>
+        <v>1730</v>
       </c>
       <c r="B7" s="6"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="3" t="s">
-        <v>1736</v>
+        <v>1731</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>1737</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="9" spans="1:4">
